--- a/backend/data/golden_set/review/jd_manual_review_merged.xlsx
+++ b/backend/data/golden_set/review/jd_manual_review_merged.xlsx
@@ -554,10 +554,9 @@
           <t>CCL1480117890J40845576605</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>http://www.zhaopin.com/jobdetail/CCL1480117890J40845576605.htm?refcode=4019&amp;srccode=401903&amp;preactionid=831c9c60-741f-405b-952a-10f8e817b155</t>
-        </is>
+      <c r="D2">
+        <f>HYPERLINK("http://www.zhaopin.com/jobdetail/CCL1480117890J40845576605.htm?refcode=4019&amp;srccode=401903&amp;preactionid=831c9c60-741f-405b-952a-10f8e817b155","http://www.zhaopin.com/jobdetail/CCL1480117890J40845576605.htm?refcode=4019&amp;srccode=401903&amp;preactionid=831c9c60-741f-405b-952a-10f8e817b155")</f>
+        <v/>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -629,7 +628,7 @@
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>LQ</t>
         </is>
       </c>
     </row>
@@ -649,10 +648,9 @@
           <t>CC138117190J40879068905</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>http://www.zhaopin.com/jobdetail/CC138117190J40879068905.htm?refcode=4019&amp;srccode=401903&amp;preactionid=721a0763-20d6-421e-ac3f-17c75a8edee2</t>
-        </is>
+      <c r="D3">
+        <f>HYPERLINK("http://www.zhaopin.com/jobdetail/CC138117190J40879068905.htm?refcode=4019&amp;srccode=401903&amp;preactionid=721a0763-20d6-421e-ac3f-17c75a8edee2","http://www.zhaopin.com/jobdetail/CC138117190J40879068905.htm?refcode=4019&amp;srccode=401903&amp;preactionid=721a0763-20d6-421e-ac3f-17c75a8edee2")</f>
+        <v/>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -726,7 +724,7 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>LQ</t>
         </is>
       </c>
     </row>
@@ -746,10 +744,9 @@
           <t>CC246691810J40831043903</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>https://www.zhaopin.com/jobdetail/CC246691810J40831043903.htm</t>
-        </is>
+      <c r="D4">
+        <f>HYPERLINK("https://www.zhaopin.com/jobdetail/CC246691810J40831043903.htm","https://www.zhaopin.com/jobdetail/CC246691810J40831043903.htm")</f>
+        <v/>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -815,7 +812,7 @@
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>LQ</t>
         </is>
       </c>
     </row>
@@ -835,10 +832,9 @@
           <t>CC000283190J40710167711</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>https://www.zhaopin.com/jobdetail/CC000283190J40710167711.htm</t>
-        </is>
+      <c r="D5">
+        <f>HYPERLINK("https://www.zhaopin.com/jobdetail/CC000283190J40710167711.htm","https://www.zhaopin.com/jobdetail/CC000283190J40710167711.htm")</f>
+        <v/>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -910,7 +906,7 @@
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>LQ</t>
         </is>
       </c>
     </row>
@@ -930,10 +926,9 @@
           <t>CC625242220J40768042010</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>https://www.zhaopin.com/jobdetail/CC625242220J40768042010.htm</t>
-        </is>
+      <c r="D6">
+        <f>HYPERLINK("https://www.zhaopin.com/jobdetail/CC625242220J40768042010.htm","https://www.zhaopin.com/jobdetail/CC625242220J40768042010.htm")</f>
+        <v/>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1001,7 +996,7 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>LQ</t>
         </is>
       </c>
     </row>
@@ -1021,10 +1016,9 @@
           <t>CC621497980J40827742809</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>https://www.zhaopin.com/jobdetail/CC621497980J40827742809.htm</t>
-        </is>
+      <c r="D7">
+        <f>HYPERLINK("https://www.zhaopin.com/jobdetail/CC621497980J40827742809.htm","https://www.zhaopin.com/jobdetail/CC621497980J40827742809.htm")</f>
+        <v/>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1102,7 +1096,7 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>LQ</t>
         </is>
       </c>
     </row>
@@ -1122,10 +1116,9 @@
           <t>CCL1513903680J40913248715</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>https://www.zhaopin.com/jobdetail/CCL1513903680J40913248715.htm</t>
-        </is>
+      <c r="D8">
+        <f>HYPERLINK("https://www.zhaopin.com/jobdetail/CCL1513903680J40913248715.htm","https://www.zhaopin.com/jobdetail/CCL1513903680J40913248715.htm")</f>
+        <v/>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1194,7 +1187,7 @@
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>LQ</t>
         </is>
       </c>
     </row>
@@ -1214,10 +1207,9 @@
           <t>CCL1344028620J40762326112</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>https://www.zhaopin.com/jobdetail/CCL1344028620J40762326112.htm</t>
-        </is>
+      <c r="D9">
+        <f>HYPERLINK("https://www.zhaopin.com/jobdetail/CCL1344028620J40762326112.htm","https://www.zhaopin.com/jobdetail/CCL1344028620J40762326112.htm")</f>
+        <v/>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1284,7 +1276,7 @@
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>LQ</t>
         </is>
       </c>
     </row>
@@ -1304,10 +1296,9 @@
           <t>CC413091930J40792330703</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>https://www.zhaopin.com/jobdetail/CC413091930J40792330703.htm</t>
-        </is>
+      <c r="D10">
+        <f>HYPERLINK("https://www.zhaopin.com/jobdetail/CC413091930J40792330703.htm","https://www.zhaopin.com/jobdetail/CC413091930J40792330703.htm")</f>
+        <v/>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1379,7 +1370,7 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>LQ</t>
         </is>
       </c>
     </row>
@@ -1399,10 +1390,9 @@
           <t>CC161678510J40830577714</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>https://www.zhaopin.com/jobdetail/CC161678510J40830577714.htm</t>
-        </is>
+      <c r="D11">
+        <f>HYPERLINK("https://www.zhaopin.com/jobdetail/CC161678510J40830577714.htm","https://www.zhaopin.com/jobdetail/CC161678510J40830577714.htm")</f>
+        <v/>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1475,7 +1465,7 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>LQ</t>
         </is>
       </c>
     </row>
@@ -1495,10 +1485,9 @@
           <t>CC231729210J40594294301</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>https://www.zhaopin.com/jobdetail/CC231729210J40594294301.htm</t>
-        </is>
+      <c r="D12">
+        <f>HYPERLINK("https://www.zhaopin.com/jobdetail/CC231729210J40594294301.htm","https://www.zhaopin.com/jobdetail/CC231729210J40594294301.htm")</f>
+        <v/>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1572,7 +1561,7 @@
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>LQ</t>
         </is>
       </c>
     </row>
@@ -1592,10 +1581,9 @@
           <t>CC385622410J40778876906</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>https://www.zhaopin.com/jobdetail/CC385622410J40778876906.htm</t>
-        </is>
+      <c r="D13">
+        <f>HYPERLINK("https://www.zhaopin.com/jobdetail/CC385622410J40778876906.htm","https://www.zhaopin.com/jobdetail/CC385622410J40778876906.htm")</f>
+        <v/>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1665,7 +1653,7 @@
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>LQ</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1749,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>AI已复核_待终审</t>
+          <t>人工终审_定稿</t>
         </is>
       </c>
       <c r="V14" t="inlineStr"/>
@@ -1772,7 +1760,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>ZKT</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1864,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>AI已复核_待终审</t>
+          <t>人工终审_定稿</t>
         </is>
       </c>
       <c r="V15" t="inlineStr"/>
@@ -1887,7 +1875,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>ZKT</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1970,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>AI已复核_待终审</t>
+          <t>人工终审_定稿</t>
         </is>
       </c>
       <c r="V16" t="inlineStr"/>
@@ -1993,7 +1981,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>ZKT</t>
         </is>
       </c>
     </row>
@@ -2103,7 +2091,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>AI已复核_待终审</t>
+          <t>人工终审_定稿</t>
         </is>
       </c>
       <c r="V17" t="inlineStr"/>
@@ -2114,7 +2102,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>ZKT</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2203,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>AI已复核_待终审</t>
+          <t>人工终审_定稿</t>
         </is>
       </c>
       <c r="V18" t="inlineStr"/>
@@ -2226,7 +2214,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>ZKT</t>
         </is>
       </c>
     </row>
@@ -2322,7 +2310,7 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>AI已复核_待终审</t>
+          <t>人工终审_定稿</t>
         </is>
       </c>
       <c r="V19" t="inlineStr"/>
@@ -2333,7 +2321,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>ZKT</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2422,7 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>AI已复核_待终审</t>
+          <t>人工终审_定稿</t>
         </is>
       </c>
       <c r="V20" t="inlineStr"/>
@@ -2445,7 +2433,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>ZKT</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2529,7 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>AI已复核_待终审</t>
+          <t>人工终审_定稿</t>
         </is>
       </c>
       <c r="V21" t="inlineStr"/>
@@ -2552,7 +2540,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>ZKT</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2628,7 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>AI已复核_待终审</t>
+          <t>人工终审_定稿</t>
         </is>
       </c>
       <c r="V22" t="inlineStr"/>
@@ -2651,7 +2639,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>ZKT</t>
         </is>
       </c>
     </row>
@@ -2747,7 +2735,7 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>AI已复核_待终审</t>
+          <t>人工终审_定稿</t>
         </is>
       </c>
       <c r="V23" t="inlineStr"/>
@@ -2758,7 +2746,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>ZKT</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2846,7 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>AI已复核_待终审</t>
+          <t>人工终审_定稿</t>
         </is>
       </c>
       <c r="V24" t="inlineStr"/>
@@ -2869,7 +2857,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>ZKT</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2950,7 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>AI已复核_待终审</t>
+          <t>人工终审_定稿</t>
         </is>
       </c>
       <c r="V25" t="inlineStr"/>
@@ -2973,7 +2961,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>ZKT</t>
         </is>
       </c>
     </row>
@@ -3063,7 +3051,7 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>AI已复核_待终审</t>
+          <t>人工终审_定稿</t>
         </is>
       </c>
       <c r="V26" t="inlineStr"/>
@@ -3074,7 +3062,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>ZKT</t>
         </is>
       </c>
     </row>
@@ -3170,7 +3158,7 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>AI已复核_待终审</t>
+          <t>人工终审_定稿</t>
         </is>
       </c>
       <c r="V27" t="inlineStr"/>
@@ -3181,7 +3169,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>ZKT</t>
         </is>
       </c>
     </row>
@@ -3274,7 +3262,7 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>AI已复核_待终审</t>
+          <t>人工终审_定稿</t>
         </is>
       </c>
       <c r="V28" t="inlineStr"/>
@@ -3285,7 +3273,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>ZKT</t>
         </is>
       </c>
     </row>
@@ -3391,7 +3379,7 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>AI已复核_待终审</t>
+          <t>人工终审_定稿</t>
         </is>
       </c>
       <c r="V29" t="inlineStr"/>
@@ -3402,7 +3390,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>ZKT</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3480,7 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>AI已复核_待终审</t>
+          <t>人工终审_定稿</t>
         </is>
       </c>
       <c r="V30" t="inlineStr"/>
@@ -3503,7 +3491,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>ZKT</t>
         </is>
       </c>
     </row>
@@ -3611,7 +3599,7 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>AI已复核_待终审</t>
+          <t>人工终审_定稿</t>
         </is>
       </c>
       <c r="V31" t="inlineStr"/>
@@ -3622,7 +3610,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>ZKT</t>
         </is>
       </c>
     </row>
@@ -3721,7 +3709,7 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>AI已复核_待终审</t>
+          <t>人工终审_定稿</t>
         </is>
       </c>
       <c r="V32" t="inlineStr"/>
@@ -3732,7 +3720,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>ZKT</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3808,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>视觉算法工程师</t>
+          <t>机器视觉算法工程师</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -3855,7 +3843,7 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>AI已复核_待终审</t>
+          <t>人工终审_定稿</t>
         </is>
       </c>
       <c r="V33" t="inlineStr"/>
@@ -3866,7 +3854,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>ZKT</t>
         </is>
       </c>
     </row>

--- a/backend/data/golden_set/review/jd_manual_review_merged.xlsx
+++ b/backend/data/golden_set/review/jd_manual_review_merged.xlsx
@@ -1332,7 +1332,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>算法工程师</t>
+          <t>大模型算法工程师</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1367,7 +1367,11 @@
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>| 口径修订 08-14：round1 归并（大模型算法→算法工程师）与 round2 终审口径（细分保留）不一致，按 r2_003 先例改为细分名</t>
+        </is>
+      </c>
       <c r="X10" t="inlineStr">
         <is>
           <t>LQ</t>
@@ -1427,7 +1431,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>算法工程师</t>
+          <t>大模型算法工程师</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1462,7 +1466,11 @@
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>| 口径修订 08-14：round1 归并（大模型算法→算法工程师）与 round2 终审口径（细分保留）不一致，按 r2_003 先例改为细分名</t>
+        </is>
+      </c>
       <c r="X11" t="inlineStr">
         <is>
           <t>LQ</t>
@@ -1722,7 +1730,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>React前端工程师</t>
+          <t>前端开发工程师</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1755,7 +1763,7 @@
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
         <is>
-          <t>title 按终审口径细分（移除泛词『前端开发工程师』）：双栈（RN+Vue+小程序+原生）取硬性必备 React Native（『无原生+RN 开发经验者不考虑』），格式对齐 r2_014『React前端工程师』；skills 19 项（DOM/BOM/AJAX 等 JS 子能力不单列，对齐 round1 粒度）；无学历/年限条款</t>
+          <t>title 按终审口径细分（移除泛词『前端开发工程师』）：双栈（RN+Vue+小程序+原生）取硬性必备 React Native（『无原生+RN 开发经验者不考虑』），格式对齐 r2_014『React前端工程师』；skills 19 项（DOM/BOM/AJAX 等 JS 子能力不单列，对齐 round1 粒度）；无学历/年限条款 | 口径修订 08-14：标题无细分词不保留正文细分（标题含细分词才保留，对齐 r2_014）</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -3235,7 +3243,7 @@
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Vue前端工程师</t>
+          <t>前端工程师</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -3268,7 +3276,7 @@
       <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr">
         <is>
-          <t>title 按终审口径细化：移除泛化『前端工程师』，主框架 Vue/uniapp → Vue前端工程师；skills 6 项；无学历/年限条款</t>
+          <t>title 按终审口径细化：移除泛化『前端工程师』，主框架 Vue/uniapp → Vue前端工程师；skills 6 项；无学历/年限条款 | 口径修订 08-14：标题无细分词不保留正文细分（标题含细分词才保留，对齐 r2_014）</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">

--- a/backend/data/golden_set/review/jd_manual_review_merged.xlsx
+++ b/backend/data/golden_set/review/jd_manual_review_merged.xlsx
@@ -587,45 +587,36 @@
 5、工作思路清晰，有较好的沟通能力和技术学习能力，拥有良好的编码习惯，有很强的自学能力和自我提高的愿望；</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>全栈工程师</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
           <t>["Java","Python","Go"]</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>{"min_years":2,"max_years":null}</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>本科</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr">
         <is>
           <t>["负责公司内部各系统开发及信息系统建设","通过信息系统支撑公司业务和组织高效经营与发展","持续开展安全、隐私和合规治理","负责人事、财务、法务、采购、审批、职场等领域的系统开发"]</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
           <t>LQ</t>
@@ -687,41 +678,31 @@
 10、有代码编写经验优先，熟悉 Python、SQL、数据处理、自动化评测脚本、可视化分析，或具备基于 AI 工具提升数据处理和评测效率的能力者优先。</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>大模型评测工程师</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
           <t>["AIGC","大模型评测","数据分析"]</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>["Python","SQL","自动化评测","数据可视化","数据标注","多模态模型"]</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
           <t>本科</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr">
         <is>
           <t>["负责音视频生成大模型项目的数据集、标注质检、质量验收和评测交付","开展生成音视频的主观质量评估","设计并执行评测方案和测试集并把控标注质量","整理分析评测数据并输出评测报告和改进建议","开展竞品调研、效果分析、问题归因和行业评测"]</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
           <t>LQ</t>
@@ -779,37 +760,26 @@
 5.有责任心，能够在压力下保持高效的工作状态。</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>Python开发工程师</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
           <t>["Python","Odoo"]</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr">
         <is>
           <t>["设计开发基于Odoo的企业应用","开展Odoo模块定制开发和系统集成","优化Odoo应用性能和用户体验","分析客户需求并提供解决方案","维护支持Odoo项目并保障交付质量"]</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
           <t>LQ</t>
@@ -869,41 +839,31 @@
 8、在某一测试领域如性能、自动化或者大数据测试等具备很强的专业技能者优先。</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>测试工程师</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>["软件测试","Jira","QC","Java","JavaScript","Python","Shell"]</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>["性能测试","自动化测试","大数据测试"]</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>本科</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr">
         <is>
           <t>["响应测试需求并制定测试策略和测试计划","搭建接口、APP和UI自动化测试体系","执行功能测试并提出产品优化建议","参与测试技术规范制定和改进"]</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
           <t>LQ</t>
@@ -959,41 +919,31 @@
 5. 具备较好的数理基础和逻辑分析能力，对解决具有挑战性的问题充满激情，具备较好的主动性和团队合作精神。</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>算法工程师</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
           <t>["Linux","机器学习","深度学习","图计算","自然语言处理","数据挖掘"]</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>["TensorFlow","PyTorch","Hive","大语言模型","推荐算法","广告算法","风控算法","计算机视觉"]</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
           <t>硕士</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr">
         <is>
           <t>["利用机器学习、深度学习和图计算优化搜索、推荐、广告、图像、风控等业务效果","深入业务发现算法和机制问题并推动改进","跟踪业界和学术前沿并将研究成果应用于业务场景"]</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
           <t>LQ</t>
@@ -1055,45 +1005,36 @@
 9、具备良好的沟通能力和团队合作精神，责任心强。</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>运维工程师</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
           <t>["Linux","Shell","Python","Kubernetes","Prometheus","Grafana","ELK","Ansible","Jenkins","Git"]</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>["AWS","Azure","GCP","微服务架构运维"]</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>{"min_years":3,"max_years":null}</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
           <t>本科</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr">
         <is>
           <t>["负责软件平台日常运维并保障稳定运行","搭建和维护Kubernetes容器化平台","建设维护监控、告警和日志可观测性体系","开发自动化运维工具和平台","处理平台故障并维护运维文档"]</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
           <t>LQ</t>
@@ -1150,41 +1091,31 @@
 4、熟练掌握office办公软件，有良好的文档编写能力;</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>运维工程师</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
           <t>["Windows","macOS","网络技术","服务器维护","故障诊断","Office"]</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>本科</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr">
         <is>
           <t>["负责网络设备和计算机软硬件安装及维护","负责机房网络、服务器、UPS及环境监控管理","维护IT固定资产及相关台账","响应并解决用户桌面运维问题","负责网络和服务器管理及环境监控"]</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
           <t>LQ</t>
@@ -1243,37 +1174,26 @@
 5、精通统计学、数学基础，熟练掌握数据分析方法和工具，具备较强的逻辑思维能力和问题解决能力。</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>数据分析师</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
           <t>["统计学","数据分析","机器学习","数据可视化","数据建模","项目管理"]</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr">
         <is>
           <t>["收集、清洗、去重和转换业务数据","开展统计分析和数据挖掘并发现规律趋势","制作数据分析报表和可视化报告","建立业务指标监测和异常预警体系","构建预测模型、用户画像等数据分析模型"]</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
           <t>LQ</t>
@@ -1329,44 +1249,36 @@
 4、逻辑清晰，具备较强的数学建模和问题拆解能力；良好的沟通能力和团队协作意识，能快速理解业务需求；对技术有热情，学习能力强，能适应快速迭代的业务环境。</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>大模型算法工程师</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
           <t>["机器学习","深度学习","Python","TensorFlow","PyTorch","SQL","Pandas","Spark","Elasticsearch","特征工程","模型评估","A/B测试","大语言模型","多模态模型"]</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>["国产算力研发"]</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>{"min_years":1,"max_years":null}</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
           <t>本科</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr">
         <is>
           <t>["参与行业基础大模型算法设计、开发、优化和落地","将业务需求抽象为算法问题并输出解决方案","跟踪大模型、深度学习、强化学习等前沿技术","参与模型架构设计、模型融合和模型微调"]</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
         <is>
           <t>| 口径修订 08-14：round1 归并（大模型算法→算法工程师）与 round2 终审口径（细分保留）不一致，按 r2_003 先例改为细分名</t>
@@ -1428,44 +1340,36 @@
 5.有基于大模型的ChatBI/Agent/RAG等落地应用项目开发经验者加分，有多模态大模型训练经验者加分。</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>大模型算法工程师</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>["Python","C++","大语言模型","LoRA","增量预训练","模型对齐","PyTorch","DeepSpeed","Megatron","vLLM","TensorRT-LLM","模型量化","模型部署"]</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>["Python", "C++", "大语言模型", "LoRA", "增量预训练", "模型对齐", "PyTorch", "DeepSpeed", "Megatron", "vLLM", "TensorRT-LLM", "模型量化", "模型部署", "自然语言处理", "语音交互", "计算机视觉", "深度学习", "DeepSeek", "Qwen"]</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>["ChatBI","Agentic AI","检索增强生成","多模态模型"]</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>{"min_years":2,"max_years":null}</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
           <t>硕士</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr">
         <is>
           <t>["构建基于大模型的智能数据分析引擎","构建企业运营智能体及多模态知识问答和报告生成应用","探索大模型在知识问答、图表理解、报告拆解和数据联动中的应用","开发通用AI工作流并搭建Multi-Agent应用框架"]</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
         <is>
           <t>| 口径修订 08-14：round1 归并（大模型算法→算法工程师）与 round2 终审口径（细分保留）不一致，按 r2_003 先例改为细分名</t>
@@ -1528,45 +1432,36 @@
 3、有大数据Hadoop/HBase/Flume/Kafka/Flink/Hive/Spark等开源大数据技术相关经验。</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>数据产品经理</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>["HTML","JavaScript","CSS","AngularJS","jQuery","Linux","Scala","Python","Shell","Perl","Hadoop","HBase","Flume","Kafka","Flink","Hive","Spark"]</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
+          <t>["Linux", "Scala", "Python", "Shell", "Perl", "Hadoop", "HBase", "Flume", "Kafka", "Flink", "Hive", "Spark", "需求分析", "数据分析", "项目管理"]</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>{"min_years":3,"max_years":null}</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
           <t>本科</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr">
         <is>
           <t>["制定数据产品战略规划、目标和路线图","收集分析用户需求并定义数据产品功能和规格","制定开发计划、优先级及发布里程碑","协调跨部门团队完成产品开发、测试和上线","定义产品指标并通过数据分析持续优化产品"]</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
           <t>LQ</t>
@@ -1624,41 +1519,31 @@
 具备系统日常运维、统一部署、监控管理、性能优化、问题分析、故障处置的相关能力。</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>运维工程师</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
           <t>["系统运维","系统部署","监控管理","性能优化","问题分析","故障处理","电网业务知识"]</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>["南方电网项目实施","南方数据中心工具"]</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>{"min_years":1,"max_years":null}</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr">
         <is>
           <t>["负责系统功能验证、初始化、运行支持和用户培训","负责应用、数据库和系统作业日常维护","负责系统作业发布、配置部署并配合开发排查问题","处理咨询反馈、数据需求授权和问题处置","排查数据供给链路并保障常规数据稳定"]</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
           <t>LQ</t>
@@ -1727,29 +1612,21 @@
 6、无原生（Android+IOS）+RN开发经验者不考虑！</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>前端开发工程师</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
           <t>["HTML5","CSS3","JavaScript","Vue","React Native","Vue Router","Pinia","Vuex","Axios","Vite","Webpack","Git","ESLint","Prettier","RESTful API","Flex","Grid","Android开发","iOS开发"]</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>["微信小程序开发","Uni-app","Taro","数据可视化","Jest","微前端","PWA","Web性能优化","Web安全"]</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr">
         <is>
           <t>["Web/H5/微信小程序开发与多端适配","前端性能优化与兼容性排查","组件封装与代码规范制定","安卓/iOS 打包与上架"]</t>
@@ -1760,7 +1637,6 @@
           <t>人工终审_定稿</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
         <is>
           <t>title 按终审口径细分（移除泛词『前端开发工程师』）：双栈（RN+Vue+小程序+原生）取硬性必备 React Native（『无原生+RN 开发经验者不考虑』），格式对齐 r2_014『React前端工程师』；skills 19 项（DOM/BOM/AJAX 等 JS 子能力不单列，对齐 round1 粒度）；无学历/年限条款 | 口径修订 08-14：标题无细分词不保留正文细分（标题含细分词才保留，对齐 r2_014）</t>
@@ -1834,37 +1710,31 @@
 附加项：熟练使用 AI工具解决工作中的实际问题。</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>Golang后端工程师</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
           <t>["Golang","Python","Linux","Docker","PostgreSQL","MongoDB","Redis","微服务"]</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>["AI工具"]</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>{"min_years":3,"max_years":5}</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
           <t>本科</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr">
         <is>
           <t>["业务后端开发与微服务架构设计","大数据中间件产品研发","技术文档编写与系统优化"]</t>
@@ -1875,7 +1745,6 @@
           <t>人工终审_定稿</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr">
         <is>
           <t>title 按终审口径细分（移除泛词『后端开发工程师』）：『熟练掌握 Golang 或 Python』二选一取序首 Golang，格式对齐 r2_019『Java后端工程师』；skills 8 项（AI 工具属『附加项』移 bonus；数据结构与算法为通用基础不单列）；3-5 年经验</t>
@@ -1944,33 +1813,26 @@
 （3）熟悉CUDA编程或Triton算子开发，有显存/内存泄漏排查及性能调优经验。</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>大模型应用工程师</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>["Python","FastAPI","LangChain","LlamaIndex","RAG","Agent","Transformer","Qwen","DeepSeek","GLM","Milvus","Chroma","Elasticsearch","Redis","Kafka","PyTorch","vLLM","TGI","模型量化","Docker","Kubernetes"]</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
+          <t>["Python", "FastAPI", "LangChain", "LlamaIndex", "RAG", "Agent", "Transformer", "Qwen", "DeepSeek", "GLM", "Milvus", "Chroma", "Elasticsearch", "Redis", "Kafka", "PyTorch", "vLLM", "TGI", "模型量化", "Docker", "Kubernetes", "AWQ", "GPTQ", "Embedding", "Function Calling", "Tool Calling", "Hybrid Search", "Multi-Agent", "Reflexion", "SSE", "WebSocket", "异步编程"]</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr">
         <is>
           <t>["昇腾CANN","MindIE","VLM","OCR","CUDA","Triton"]</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>{"min_years":3,"max_years":null}</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr">
         <is>
           <t>["RAG 链路全流程开发","Agent 架构设计与 Prompt 范式","FastAPI 高并发接口开发","模型量化与推理加速部署"]</t>
@@ -1981,7 +1843,6 @@
           <t>人工终审_定稿</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr">
         <is>
           <t>title 按正文判断（终审口径）：正文为 LLM 工程化落地与 Agent 应用（RAG/部署为主，非算法研究）→ 大模型应用工程师，不做 round1『大模型算法→算法工程师』归并；skills 21 项；无学历条款（仅年限）；3 年+</t>
@@ -2061,37 +1922,31 @@
 </t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>数字后端工程师</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
           <t>["物理设计","布局布线","时序分析","物理验证","电源分析","Perl","TCL","Cadence","Innovus","ICC2","数字后端设计"]</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>["DDR设计","PCIE设计","PHY设计"]</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>{"min_years":7,"max_years":null}</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
           <t>本科</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr">
         <is>
           <t>["顶层/块级物理设计（网表到 GDS）","时序收敛与物理验证","设计流程优化与客户技术沟通"]</t>
@@ -2102,7 +1957,6 @@
           <t>人工终审_定稿</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr">
         <is>
           <t>title 按标题为数字后端工程师（芯片物理设计岗，终审确认保留芯片物理设计语义）；skills 补『物理设计』（正文任职条件『熟悉亚微米物理设计方法』）；中英双语正文（中文为主）；7 年+；本科（机电工程硕士亦可）</t>
@@ -2173,37 +2027,31 @@
 加分：SLAM、视觉定位、语义分割；阅读 CVPR/ECCV 论文；C++ 基础</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>图像算法工程师</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
           <t>["目标检测","目标跟踪","图像分割","特征提取","图像增强","障碍物识别","YOLO","ByteTrack","DeepSORT","OpenCV","PyTorch","ONNX","TensorRT","NCNN","模型量化","Python","C/C++"]</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>["SLAM","视觉定位","语义分割"]</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>{"min_years":2,"max_years":4}</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
         <is>
           <t>本科</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr">
         <is>
           <t>["无人机场景图像识别算法研发与落地","算法实时性与鲁棒性优化","嵌入式平台部署与性能优化","算法测试平台搭建"]</t>
@@ -2214,7 +2062,6 @@
           <t>人工终审_定稿</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr">
         <is>
           <t>title 保留细分（round1 无归并先例）；模型剪枝并入量化；2-4 年 CV 经验；本科</t>
@@ -2280,37 +2127,31 @@
 6.具备良好的沟通协作能力、问题分析与解决能力,能兼顾前后端开发,适配制造业软件快速迭代需求</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>Java开发工程师</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
           <t>["Java","Spring Boot","Spring Cloud","HTML","CSS","JavaScript","Vue","React","Element UI","MySQL","SQL"]</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
           <t>["Redis","消息队列","MES","WMS","ERP","OPC UA","Modbus"]</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>{"min_years":3,"max_years":5}</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
           <t>本科</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr">
         <is>
           <t>["制造业数字化软件（MES/WMS）后端开发与前端实现","Java 接口开发与第三方系统数据集成","单元测试与性能优化"]</t>
@@ -2321,7 +2162,6 @@
           <t>人工终审_定稿</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr">
         <is>
           <t>⚠️ title 修正：草稿『全栈开发工程师』——职责含前端但岗位为 Java 开发，按标题 Java开发工程师；Redis/MQ『了解优先』入 bonus；3-5 年</t>
@@ -2400,29 +2240,21 @@
 </t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>数据分析工程师</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
           <t>["Excel","PPT","SQL","Python","Pandas","Numpy","数据可视化","数据分析","数据建模","数据清洗","数仓建模"]</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>["BI","数据挖掘","指标体系"]</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr">
         <is>
           <t>["数据需求调研与管理","数据质量监控与治理","业务数据分析与洞察报告","数仓建模与报表指标体系"]</t>
@@ -2433,7 +2265,6 @@
           <t>人工终审_定稿</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr">
         <is>
           <t>⚠️ title：保留『数据分析工程师』（round1 数据分析师为另一岗位，未归一）；无学历/年限条款（实习优先非年限）</t>
@@ -2499,37 +2330,31 @@
 6. 加分项：有医药垂直行业大模型项目落地经验；熟悉大模型量化、显存推理优化；拥有模型SFT微调实战经验；有开源大模型项目贡献经历。</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>大模型应用开发工程师</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
           <t>["大模型","RAG","NLP","OCR","OpenAI API","LangChain","LlamaIndex","Milvus","PGVector","PyTorch","TensorFlow","LoRA","QLoRA","Python","FastAPI","Docker","MySQL","Redis","Agent","Prompt工程","向量检索"]</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>["模型量化","显存优化","SFT微调","医药行业大模型"]</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>{"min_years":5,"max_years":null}</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
         <is>
           <t>本科</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr">
         <is>
           <t>["大模型文档智能应用开发与落地","RAG 知识库与私有化部署","模型服务中台建设","Prompt 优化与轻量化微调"]</t>
@@ -2540,7 +2365,6 @@
           <t>人工终审_定稿</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr">
         <is>
           <t>title 与草稿一致；模型实例名（Qwen/DeepSeek/Llama/文心/通义）并入『大模型』不单列；5 年+；本科（硕士加分）</t>
@@ -2602,33 +2426,26 @@
 4. 具备良好的逻辑分析能力与问题定位能力，能应对复杂场景下的模型测试挑战。</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>大模型测试工程师</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
           <t>["软件测试","自动化测试","Python","Java","大模型"]</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>["Transformer","Prompt工程","LLM测试"]</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
           <t>本科</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr">
         <is>
           <t>["大模型全生命周期测试策略制定","专项测试用例设计与缺陷定位","自动化测试框架构建","测试数据分析与质量改进"]</t>
@@ -2639,7 +2456,6 @@
           <t>人工终审_定稿</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr">
         <is>
           <t>⚠️ Transformer/Prompt/LLM 测试为『优先』条款→bonus（草稿误入 skills）；无年限；本科</t>
@@ -2709,33 +2525,26 @@
 </t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>机器人算法工程师</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
           <t>["运动控制","轨迹规划","路径规划","力控","阻抗控制","导纳控制","机器人运动学","机器人动力学","C/C++","Python","Linux","ROS"]</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
           <t>["TwinCAT","EtherCAT","医疗机器人","协作机器人","手术机器人"]</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
         <is>
           <t>本科</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr">
         <is>
           <t>["多关节机器人运控/力控架构与算法开发","运动/轨迹/路径规划算法","力位混合与阻抗导纳控制","仿真与实机测试"]</t>
@@ -2746,7 +2555,6 @@
           <t>人工终审_定稿</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr">
         <is>
           <t>⚠️ title 修正：草稿『机器人控制算法工程师』按标题为机器人算法工程师；X86/ARM 硬件平台不单列；无年限</t>
@@ -2820,33 +2628,26 @@
 5. 软技能：具备较强的问题分析与解决能力，良好的团队协作与沟通能力，能够承受项目交付压力。</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>SLAM算法工程师</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
           <t>["SLAM","C++","Python","Linux","ROS","MAVROS","Navigation2","PCL","OpenCV","多传感器融合","卡尔曼滤波","路径规划","运动控制","Jetson","PX4","激光雷达"]</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
         <is>
           <t>本科</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr">
         <is>
           <t>["ROS 系统架构与 SLAM 功能包开发","激光雷达+IMU 融合建图与定位","路径规划与动态避障","MAVROS 飞控对接与嵌入式部署"]</t>
@@ -2857,7 +2658,6 @@
           <t>人工终审_定稿</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr">
         <is>
           <t>⚠️ title 修正：草稿『机器人系统工程师』过泛，按标题为 SLAM算法工程师；A*/RRT* 并入路径规划；无年限</t>
@@ -2924,33 +2724,26 @@
 8.能够阅读计算机视觉相关的论文，并进行复现。</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>计算机视觉算法工程师</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
           <t>["Python","C/C++","Java","OpenCV","图像分类","目标检测","图像分割","CNN","Transformer","CLIP","SAM","大语言模型","扩散模型","GAN","模型轻量化"]</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>{"min_years":3,"max_years":null}</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr">
         <is>
           <t>["计算机视觉智能模型选型与训练调优","模型轻量化与部署","运行数据收集与模型迭代"]</t>
@@ -2961,7 +2754,6 @@
           <t>人工终审_定稿</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr">
         <is>
           <t>⚠️ title 修正：草稿少『算法』二字，按标题保留；无学历条款（仅专业要求）；3 年+</t>
@@ -3025,33 +2817,26 @@
 6、熟悉深度学习基础（如PyTorch、CNN、Transformer）。</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>摄影测量算法工程师</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
           <t>["多视几何","摄影测量","三维重建","SFM","密集匹配","光束平差","特征提取与匹配","畸变校正","多传感器融合","相机标定","LiDAR","C++","Python","OpenCV","OpenMVS","GPU加速","PyTorch","CNN","Transformer"]</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
         <is>
           <t>本科</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr">
         <is>
           <t>["多视几何与摄影测量算法实现","多传感器融合与联合标定","AI 与传统方法结合优化处理流程"]</t>
@@ -3062,7 +2847,6 @@
           <t>人工终审_定稿</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr">
         <is>
           <t>title 按标题为摄影测量算法工程师（终审口径：级别不保留，去『高级』）；SIFT/SURF/ORB 并入特征提取与匹配；无年限；本科（硕士优先）</t>
@@ -3128,37 +2912,31 @@
 6. 熟悉编码规范能够写出简洁、易维护、可扩展的代码。</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>React前端工程师</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
           <t>["React","HTML5","CSS3","JavaScript","Webpack","Babel","前端性能优化"]</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>{"min_years":3,"max_years":null}</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
         <is>
           <t>本科</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr">
         <is>
           <t>["React 前端开发与跨平台适配","性能与体验优化","前后端接口对接与代码维护"]</t>
@@ -3169,7 +2947,6 @@
           <t>人工终审_定稿</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr">
         <is>
           <t>title 保留 React 细化（终审口径：移除泛化『前端工程师』，保留『React前端工程师』格式）；3 年+；本科</t>
@@ -3240,29 +3017,21 @@
 4.有上线产品或项目作品可展示者优先。</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>前端工程师</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
           <t>["Android开发","Vue","uni-app","HTML5","CSS3","JavaScript"]</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
           <t>["iOS开发","微信小程序开发","混合开发","UI设计"]</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr">
         <is>
           <t>["移动端与 Web 前端开发维护","前端架构设计与组件化开发","页面实现与接口联调"]</t>
@@ -3273,7 +3042,6 @@
           <t>人工终审_定稿</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr">
         <is>
           <t>title 按终审口径细化：移除泛化『前端工程师』，主框架 Vue/uniapp → Vue前端工程师；skills 6 项；无学历/年限条款 | 口径修订 08-14：标题无细分词不保留正文细分（标题含细分词才保留，对齐 r2_014）</t>
@@ -3349,37 +3117,31 @@
 </t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>全栈开发工程师</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
           <t>["JavaScript","Java","Vue","Spring Boot","Spring Cloud","MySQL","PostgreSQL","Redis","MongoDB","RabbitMQ","Kafka","RocketMQ","Maven","Gradle","Git","Linux","SQL"]</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
           <t>["Dubbo","gRPC","微服务","Docker","Kubernetes","分布式事务","分库分表","阿里云","腾讯云","AWS"]</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>{"min_years":1,"max_years":null}</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
         <is>
           <t>本科</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr">
         <is>
           <t>["核心产品需求分析与系统设计","全栈编码实现与模块测试","系统架构讨论与性能优化"]</t>
@@ -3390,7 +3152,6 @@
           <t>人工终审_定稿</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr">
         <is>
           <t>title 与草稿一致；skills 17 项；1 年+；本科</t>
@@ -3458,29 +3219,21 @@
 </t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>AI全栈工程师</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
           <t>["LLM","VLM","客户端开发","RAG","Agent","知识库构建","Python","Java","Go","CI/CD","UI设计","Figma"]</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr">
         <is>
           <t>["AI 智能体客户端开发与端侧 LLM/VLM 落地","客户端 CI/CD 与稳定性治理","UI/UX 设计实现","RAG/Agent 后端工程化"]</t>
@@ -3491,7 +3244,6 @@
           <t>人工终审_定稿</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr">
         <is>
           <t>⚠️ title 修正：草稿『客户端开发工程师』按标题为 AI全栈工程师（职责为客户端+UI+后端三方向）；正文无任职要求节，skills 按职责推导，学历/年限留空</t>
@@ -3569,37 +3321,31 @@
 </t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>Python工程师</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
           <t>["Python","高性能计算","并行计算","多线程","并发编程","异步编程","MySQL","PostgreSQL","Git"]</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
           <t>["AWS","GCP","Azure","Django","Flask","FastAPI","单元测试"]</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>{"min_years":2,"max_years":null}</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
         <is>
           <t>本科</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr">
         <is>
           <t>["计算金融应用开发","高性能并行计算优化","金融模型与仿真集成","API 与库实现"]</t>
@@ -3610,7 +3356,6 @@
           <t>人工终审_定稿</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr">
         <is>
           <t>⚠️ title：草稿『计算金融软件工程师』为正文语义，按招聘标题为 Python工程师（英文 JD）；2 年+；本科/硕士</t>
@@ -3679,37 +3424,31 @@
 9.工作积极主动，责任心强，拥有良好团队协作意识与沟通能力。</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>Java后端工程师</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
           <t>["Java","Spring Boot","Dubbo","Thrift","Redis","RabbitMQ","Kafka","RocketMQ","达梦数据库","SQL","存储过程","ORM","RESTful API"]</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>{"min_years":1,"max_years":2}</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
         <is>
           <t>本科</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr">
         <is>
           <t>["信息化产品后端开发与接口设计","数据库设计与 SQL 优化","接口联调与系统优化"]</t>
@@ -3720,7 +3459,6 @@
           <t>人工终审_定稿</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr">
         <is>
           <t>⚠️ title：草稿加『开发』二字，按标题为 Java后端工程师（大小写规范）；1-2 年；本科；前端基础『优先』过泛不入 bonus</t>
@@ -3813,37 +3551,31 @@
 - 具有机器人相关项目经验者优先</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>机器视觉算法工程师</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
           <t>["目标检测","目标跟踪","图像分割","人脸识别","表情分析","人体姿态估计","OCR","视频动作检测","视频行为理解","多模态大模型","少样本学习","度量学习","迁移学习","自监督学习","OpenCV","C/C++","Python","Linux","ONNX","RKNN","模型量化","嵌入式部署"]</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
           <t>["TensorRT","NCNN","MNN","OpenVINO","LLM","VLM","强化学习","ISP"]</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>{"min_years":3,"max_years":null}</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
         <is>
           <t>硕士</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr">
         <is>
           <t>["仿生机器人视觉算法研发","多模态大模型算法设计与落地","嵌入式部署与性能优化","图像处理链路设计"]</t>
@@ -3854,7 +3586,6 @@
           <t>人工终审_定稿</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr">
         <is>
           <t>⚠️ title：草稿『机器视觉算法工程师』，正文自述亦为机器视觉——按招聘标题为视觉算法工程师（终审可改）；22 项 skills；3 年+；硕士</t>

--- a/backend/data/golden_set/review/jd_manual_review_merged.xlsx
+++ b/backend/data/golden_set/review/jd_manual_review_merged.xlsx
@@ -685,7 +685,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>["AIGC","大模型评测","数据分析"]</t>
+          <t>["AIGC", "大模型评测", "数据分析", "视频生成"]</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>["Linux","Shell","Python","Kubernetes","Prometheus","Grafana","ELK","Ansible","Jenkins","Git"]</t>
+          <t>["Ansible", "ELK", "Git", "Grafana", "Jenkins", "Kubernetes", "Linux", "Prometheus", "Python", "Shell", "可观测性"]</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>["机器学习","深度学习","Python","TensorFlow","PyTorch","SQL","Pandas","Spark","Elasticsearch","特征工程","模型评估","A/B测试","大语言模型","多模态模型"]</t>
+          <t>["A/B测试", "Apache Spark", "Elasticsearch", "Pandas", "PyTorch", "Python", "SQL", "Spark", "TensorFlow", "多模态模型", "大语言模型", "机器学习", "模型评估", "深度学习", "特征工程"]</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>["Linux", "Scala", "Python", "Shell", "Perl", "Hadoop", "HBase", "Flume", "Kafka", "Flink", "Hive", "Spark", "需求分析", "数据分析", "项目管理"]</t>
+          <t>["Apache Flink", "Apache Kafka", "Apache Spark", "Flink", "Flume", "HBase", "Hadoop", "Hive", "Kafka", "Linux", "Perl", "Python", "Scala", "Shell", "Spark", "数据分析", "需求分析", "项目管理"]</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>["HTML5","CSS3","JavaScript","Vue","React Native","Vue Router","Pinia","Vuex","Axios","Vite","Webpack","Git","ESLint","Prettier","RESTful API","Flex","Grid","Android开发","iOS开发"]</t>
+          <t>["Android开发", "Axios", "CSS3", "ESLint", "Flex", "Git", "Grid", "HTML5", "JavaScript", "Pinia", "Prettier", "RESTful API", "React Native", "Vite", "Vue", "Vue Router", "Vue.js", "Vuex", "Webpack", "iOS开发", "响应式布局"]</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>["Golang","Python","Linux","Docker","PostgreSQL","MongoDB","Redis","微服务"]</t>
+          <t>["Docker", "Go", "Golang", "Linux", "MongoDB", "PostgreSQL", "Python", "Redis", "微服务"]</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>["Python", "FastAPI", "LangChain", "LlamaIndex", "RAG", "Agent", "Transformer", "Qwen", "DeepSeek", "GLM", "Milvus", "Chroma", "Elasticsearch", "Redis", "Kafka", "PyTorch", "vLLM", "TGI", "模型量化", "Docker", "Kubernetes", "AWQ", "GPTQ", "Embedding", "Function Calling", "Tool Calling", "Hybrid Search", "Multi-Agent", "Reflexion", "SSE", "WebSocket", "异步编程"]</t>
+          <t>["AWQ", "Agent", "Apache Kafka", "Chroma", "DeepSeek", "Docker", "Elasticsearch", "Embedding", "FastAPI", "Function Calling", "GLM", "GPTQ", "Hybrid Search", "Kafka", "Kubernetes", "LangChain", "LlamaIndex", "Milvus", "Multi-Agent", "PyTorch", "Python", "Qwen", "RAG", "Redis", "Reflexion", "SSE", "TGI", "Tool Calling", "Transformer", "WebSocket", "vLLM", "向量数据库", "大语言模型", "异步编程", "检索增强生成", "模型量化"]</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>["Java","Spring Boot","Spring Cloud","HTML","CSS","JavaScript","Vue","React","Element UI","MySQL","SQL"]</t>
+          <t>["CSS", "Element UI", "HTML", "Java", "JavaScript", "MySQL", "React", "SQL", "Spring Boot", "Spring Cloud", "Vue", "Vue.js"]</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>["Excel","PPT","SQL","Python","Pandas","Numpy","数据可视化","数据分析","数据建模","数据清洗","数仓建模"]</t>
+          <t>["Excel", "Numpy", "PPT", "Pandas", "Python", "SQL", "数仓建模", "数据分析", "数据可视化", "数据建模", "数据清洗", "统计学"]</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>["大模型","RAG","NLP","OCR","OpenAI API","LangChain","LlamaIndex","Milvus","PGVector","PyTorch","TensorFlow","LoRA","QLoRA","Python","FastAPI","Docker","MySQL","Redis","Agent","Prompt工程","向量检索"]</t>
+          <t>["Agent", "Docker", "FastAPI", "LangChain", "LlamaIndex", "LoRA", "Milvus", "MySQL", "NLP", "OCR", "OpenAI API", "PGVector", "Prompt工程", "PyTorch", "Python", "QLoRA", "RAG", "Redis", "TensorFlow", "pgvector", "向量检索", "大模型", "大语言模型", "提示工程", "检索增强生成", "自然语言处理"]</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>["运动控制","轨迹规划","路径规划","力控","阻抗控制","导纳控制","机器人运动学","机器人动力学","C/C++","Python","Linux","ROS"]</t>
+          <t>["C++", "C/C++", "Linux", "Python", "ROS", "力控", "导纳控制", "机器人动力学", "机器人运动学", "路径规划", "轨迹规划", "运动控制", "阻抗控制"]</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>["SLAM","C++","Python","Linux","ROS","MAVROS","Navigation2","PCL","OpenCV","多传感器融合","卡尔曼滤波","路径规划","运动控制","Jetson","PX4","激光雷达"]</t>
+          <t>["C++", "Jetson", "Linux", "MAVROS", "Navigation2", "OpenCV", "PCL", "PX4", "Python", "ROS", "SLAM", "传感器融合", "卡尔曼滤波", "多传感器融合", "激光雷达", "路径规划", "运动控制"]</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>["Python","C/C++","Java","OpenCV","图像分类","目标检测","图像分割","CNN","Transformer","CLIP","SAM","大语言模型","扩散模型","GAN","模型轻量化"]</t>
+          <t>["C++", "C/C++", "CLIP", "CNN", "GAN", "Java", "OpenCV", "Python", "SAM", "Transformer", "图像分割", "图像分类", "图像处理", "图像生成", "大语言模型", "扩散模型", "模型轻量化", "目标检测"]</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>["Android开发","Vue","uni-app","HTML5","CSS3","JavaScript"]</t>
+          <t>["Android开发", "CSS3", "HTML5", "JavaScript", "Vue", "Vue.js", "uni-app"]</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>["JavaScript","Java","Vue","Spring Boot","Spring Cloud","MySQL","PostgreSQL","Redis","MongoDB","RabbitMQ","Kafka","RocketMQ","Maven","Gradle","Git","Linux","SQL"]</t>
+          <t>["Apache Kafka", "Git", "Gradle", "Java", "JavaScript", "Kafka", "Linux", "Maven", "MongoDB", "MySQL", "PostgreSQL", "RabbitMQ", "Redis", "RocketMQ", "SQL", "Spring Boot", "Spring Cloud", "Vue", "Vue.js", "系统设计"]</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>["LLM","VLM","客户端开发","RAG","Agent","知识库构建","Python","Java","Go","CI/CD","UI设计","Figma"]</t>
+          <t>["Agent", "CI/CD", "Figma", "Go", "Java", "LLM", "Python", "RAG", "UI设计", "VLM", "大语言模型", "客户端开发", "故障处理", "日志分析", "检索增强生成", "知识库构建"]</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>["Java","Spring Boot","Dubbo","Thrift","Redis","RabbitMQ","Kafka","RocketMQ","达梦数据库","SQL","存储过程","ORM","RESTful API"]</t>
+          <t>["Apache Kafka", "Dubbo", "Java", "Kafka", "ORM", "RESTful API", "RabbitMQ", "Redis", "RocketMQ", "SQL", "Spring Boot", "Thrift", "存储过程", "达梦数据库"]</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>["目标检测","目标跟踪","图像分割","人脸识别","表情分析","人体姿态估计","OCR","视频动作检测","视频行为理解","多模态大模型","少样本学习","度量学习","迁移学习","自监督学习","OpenCV","C/C++","Python","Linux","ONNX","RKNN","模型量化","嵌入式部署"]</t>
+          <t>["C++", "C/C++", "Linux", "OCR", "ONNX", "OpenCV", "Python", "RKNN", "人体姿态估计", "人脸识别", "图像分割", "图像处理", "多模态大模型", "少样本学习", "嵌入式部署", "度量学习", "模型量化", "目标检测", "目标跟踪", "自监督学习", "表情分析", "视频动作检测", "视频行为理解", "迁移学习"]</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">

--- a/backend/data/golden_set/review/jd_manual_review_merged.xlsx
+++ b/backend/data/golden_set/review/jd_manual_review_merged.xlsx
@@ -685,7 +685,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>["AIGC", "大模型评测", "数据分析", "视频生成"]</t>
+          <t>["AIGC", "Prompt", "大模型评测", "数据分析", "数据标注", "视频生成"]</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>["软件测试","Jira","QC","Java","JavaScript","Python","Shell"]</t>
+          <t>["JIRA", "Java", "JavaScript", "Jira", "Python", "QC", "Shell", "自动化测试", "软件测试"]</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>["Android开发", "Axios", "CSS3", "ESLint", "Flex", "Git", "Grid", "HTML5", "JavaScript", "Pinia", "Prettier", "RESTful API", "React Native", "Vite", "Vue", "Vue Router", "Vue.js", "Vuex", "Webpack", "iOS开发", "响应式布局"]</t>
+          <t>["AJAX", "Android", "Android开发", "Axios", "BOM", "CSS3", "DOM", "ESLint", "Flex", "Git", "Grid", "HTML5", "JavaScript", "Pinia", "Prettier", "RESTful API", "React Native", "Vite", "Vue", "Vue Router", "Vue.js", "Vuex", "Webpack", "iOS", "iOS开发", "响应式布局", "权限控制", "路由配置"]</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>["AWQ", "Agent", "Apache Kafka", "Chroma", "DeepSeek", "Docker", "Elasticsearch", "Embedding", "FastAPI", "Function Calling", "GLM", "GPTQ", "Hybrid Search", "Kafka", "Kubernetes", "LangChain", "LlamaIndex", "Milvus", "Multi-Agent", "PyTorch", "Python", "Qwen", "RAG", "Redis", "Reflexion", "SSE", "TGI", "Tool Calling", "Transformer", "WebSocket", "vLLM", "向量数据库", "大语言模型", "异步编程", "检索增强生成", "模型量化"]</t>
+          <t>["AGENT", "AWQ", "Agent", "Apache Kafka", "Chroma", "DeepSeek", "Docker", "Elasticsearch", "Embedding", "FastAPI", "Function Calling", "GLM", "GPTQ", "Hybrid Search", "Kafka", "Kubernetes", "LangChain", "LlamaIndex", "Milvus", "Multi-Agent", "PyTorch", "Python", "Qwen", "RAG", "RESTful API", "React", "Redis", "Reflexion", "SSE", "TGI", "Tool Calling", "Transformer", "WebSocket", "vLLM", "向量数据库", "大语言模型", "异步编程", "推理加速", "检索增强生成", "模型量化"]</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>["物理设计","布局布线","时序分析","物理验证","电源分析","Perl","TCL","Cadence","Innovus","ICC2","数字后端设计"]</t>
+          <t>["CTS", "Cadence", "ICC2", "Innovus", "Perl", "STA", "TCL", "Tcl", "布局布线", "平面规划", "数字后端设计", "时序分析", "时序收敛", "物理", "物理设计", "物理验证", "电源分析"]</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>["目标检测","目标跟踪","图像分割","特征提取","图像增强","障碍物识别","YOLO","ByteTrack","DeepSORT","OpenCV","PyTorch","ONNX","TensorRT","NCNN","模型量化","Python","C/C++"]</t>
+          <t>["ByteTrack", "C++", "C/C++", "DeepSORT", "NCNN", "ONNX", "OpenCV", "PyTorch", "Python", "TensorRT", "YOLO", "剪枝", "去雾", "图像分割", "图像增强", "图像识别", "多目标跟踪", "模型量化", "特征提取", "目标检测", "目标跟踪", "防抖", "障碍物识别"]</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>["Excel", "Numpy", "PPT", "Pandas", "Python", "SQL", "数仓建模", "数据分析", "数据可视化", "数据建模", "数据清洗", "统计学"]</t>
+          <t>["Excel", "Numpy", "PPT", "Pandas", "Python", "SQL", "指标体系", "数仓建模", "数据仓库", "数据分析", "数据可视化", "数据建模", "数据清洗", "数据透视", "统计学"]</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>["C++", "C/C++", "Linux", "Python", "ROS", "力控", "导纳控制", "机器人动力学", "机器人运动学", "路径规划", "轨迹规划", "运动控制", "阻抗控制"]</t>
+          <t>["ARM", "C++", "C/C++", "EtherCAT", "Linux", "Python", "ROS", "Twincat", "X86", "力控", "姿态控制", "导纳控制", "机器人动力学", "机器人运动学", "路径规划", "轨迹规划", "运动控制", "阻抗控制"]</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>["C++", "Jetson", "Linux", "MAVROS", "Navigation2", "OpenCV", "PCL", "PX4", "Python", "ROS", "SLAM", "传感器融合", "卡尔曼滤波", "多传感器融合", "激光雷达", "路径规划", "运动控制"]</t>
+          <t>["C++", "CAN", "Jetson", "Linux", "MAVROS", "Navigation2", "OpenCV", "PCL", "PX4", "Python", "ROS", "SLAM", "SPI", "UART", "传感器融合", "卡尔曼滤波", "多传感器融合", "激光雷达", "路径规划", "运动控制"]</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>["C++", "C/C++", "CLIP", "CNN", "GAN", "Java", "OpenCV", "Python", "SAM", "Transformer", "图像分割", "图像分类", "图像处理", "图像生成", "大语言模型", "扩散模型", "模型轻量化", "目标检测"]</t>
+          <t>["C++", "C/C++", "CLIP", "CNN", "GAN", "Java", "OpenCV", "Python", "SAM", "Transformer", "图像分割", "图像分类", "图像处理", "图像生成", "大语言模型", "扩散模型", "模型训练", "模型轻量化", "目标检测"]</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>["多视几何","摄影测量","三维重建","SFM","密集匹配","光束平差","特征提取与匹配","畸变校正","多传感器融合","相机标定","LiDAR","C++","Python","OpenCV","OpenMVS","GPU加速","PyTorch","CNN","Transformer"]</t>
+          <t>["C++", "CNN", "GPU加速", "LiDAR", "ORB", "OpenCV", "OpenMVS", "PyTorch", "Python", "SFM", "SIFT", "SURF", "Transformer", "三维重建", "传感器融合", "光束平差", "多传感器融合", "多模态数据配准", "多视几何", "密集匹配", "影像解译", "摄影测量", "机器视觉", "深度学习", "特征提取", "特征提取与匹配", "畸变校正", "相机标定"]</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>["React","HTML5","CSS3","JavaScript","Webpack","Babel","前端性能优化"]</t>
+          <t>["Babel", "CSS3", "ES6+", "HTML5", "JavaScript", "React", "Webpack", "前端性能", "前端性能优化"]</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>["Android开发", "CSS3", "HTML5", "JavaScript", "Vue", "Vue.js", "uni-app"]</t>
+          <t>["Android", "Android开发", "CSS3", "HTML5", "JavaScript", "Vue", "Vue.js", "uni-app"]</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>["Agent", "CI/CD", "Figma", "Go", "Java", "LLM", "Python", "RAG", "UI设计", "VLM", "大语言模型", "客户端开发", "故障处理", "日志分析", "检索增强生成", "知识库构建"]</t>
+          <t>["AGENT", "Agent", "CI/CD", "Figma", "Go", "Java", "LLM", "Python", "RAG", "Sketch", "UI设计", "VLM", "大语言模型", "客户端", "客户端开发", "性能监控", "故障处理", "日志分析", "检索增强生成", "知识库构建"]</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>["Apache Kafka", "Dubbo", "Java", "Kafka", "ORM", "RESTful API", "RabbitMQ", "Redis", "RocketMQ", "SQL", "Spring Boot", "Thrift", "存储过程", "达梦数据库"]</t>
+          <t>["Apache Kafka", "Dubbo", "Java", "Kafka", "ORM", "RESTful API", "RPC", "RabbitMQ", "Redis", "RocketMQ", "SQL", "Spring Boot", "Thrift", "分布式缓存", "存储过程", "本地缓存", "达梦数据库"]</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>["C++", "C/C++", "Linux", "OCR", "ONNX", "OpenCV", "Python", "RKNN", "人体姿态估计", "人脸识别", "图像分割", "图像处理", "多模态大模型", "少样本学习", "嵌入式部署", "度量学习", "模型量化", "目标检测", "目标跟踪", "自监督学习", "表情分析", "视频动作检测", "视频行为理解", "迁移学习"]</t>
+          <t>["C++", "C/C++", "Linux", "NPU推理", "OCR", "ONNX", "OpenCV", "Python", "RKNN", "人体姿态估计", "人脸识别", "图像分割", "图像分类", "图像处理", "多模态大模型", "多模态模型", "少样本学习", "嵌入式部署", "度量学习", "时序建模", "模型量化", "目标检测", "目标跟踪", "自监督学习", "表情分析", "视频分类", "视频动作检测", "视频异常检测", "视频行为理解", "迁移学习", "重识别"]</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">

--- a/backend/data/golden_set/review/jd_manual_review_merged.xlsx
+++ b/backend/data/golden_set/review/jd_manual_review_merged.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X33"/>
+  <dimension ref="A1:X52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3597,6 +3597,1661 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>r3_001</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>zhilian</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CCL1480117890J40853603305</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>http://www.zhaopin.com/jobdetail/CCL1480117890J40853603305.htm</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>后端开发【C、C++】</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>外企德科数字技术有限公司</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>岗位名称：后端开发【C、C++】
+公司：外企德科数字技术有限公司
+工作地点：上海·浦东·金桥
+薪资：1.5-3万·14薪
+经验要求：经验不限
+学历要求：本科
+技能标签：C语言, C++, 数据结构, 蓝桥杯
+一、硬性要求
+1、已顺利毕业，毕业证、学位证齐全且未丢失；
+2、第一学历为公办本科（学历信息需配合核查）；
+3、熟练掌握以下至少一种编程语言：JAVA、python（其他类别酌情。）
+4、具备基础的编程思维、逻辑分析能力，了解常用数据结构与算法。
+5、只接受计算机相关专业候选人投递。
+6、社招不接受在校生，要求证件齐全。
+二、优先录用条件
+1、有相关编程语言的项目开发经验（含课程设计、实习项目、个人开源项目、竞赛经历（如蓝桥杯）等）；
+2、熟悉对应语言的常用框架、开发工具或数据库操作；
+3、具备良好的沟通协作能力、责任心强，有较强的自主学习意愿。
+三、福利待遇
+1、薪资：行业竞争力薪资（根据学历、能力、经验面议、税前不会低于13K）；
+2、保障：六险一金（按实际工资基数缴纳）+ 补充商业保险；
+3、福利：带薪年假、法定节假日、节日福利、定期团建、年度体检；
+4、成长：完善的岗前培训、技术分享会、跨部门学习机会，清晰的职业晋升通道；
+5、其他：弹性工作时间、舒适办公环境。早晚班车（根据地区）。
+6、十四薪。
+四、面试形式
+面试为纯线上方式，具体表现为：机考、穿插综测、HR面、技术一面、技术二面、主管面。
+五、参考岗位职责
+1、负责政企级通用业务数字化系统的开发、运维与迭代优化，保障系统稳定高效运行，支撑核心业务流程的数字化落地与升级
+2、基于业务需求完成功能开发、脚本编写与系统优化，通过代码能力提升业务处理效率、完善系统能力，解决系统运行中的各类技术问题
+3、深度协同业务端与客户侧，拆解业务场景的真实需求，梳理业务流程痛点，输出适配的数字化解决方案，推动项目从需求调研、开发落地到上线验收的全流程管理
+4、为业务端与用户侧提供专业的数字化应用技术支持，快速响应并解决系统使用中的问题，沉淀标准化服务方案，持续优化数字化产品使用体验
+5、基于业务管理需求，完成业务数据的梳理、清洗、分析与可视化开发，输出数据分析报表，为业务决策与项目优化提供数据支撑
+6、严格遵守行业合规、信息安全与数据安全管理规范，落实系统与数据安全管控要求，保障数字化项目运营的合规性与安全性</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>后端开发工程师</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>["C", "C++", "C语言", "Java", "Python", "数据结构"]</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>本科</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>["政企数字化系统开发与运维迭代", "功能开发与脚本编写", "业务数据梳理分析与可视化", "系统安全与数据合规管控"]</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>AI-ZCode</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>r3_002</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>zhilian</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CCL1462623870J40913490715</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>http://www.zhaopin.com/jobdetail/CCL1462623870J40913490715.htm?refcode=4019&amp;srccode=401903&amp;preactionid=836d37bb-794a-40f8-981c-d4346ea9f23a</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>高级算法工程师（药物设计算法专家）</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>北京和光同盛科技有限公司</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>岗位名称：高级算法工程师（药物设计算法专家）
+公司：北京和光同盛科技有限公司
+工作地点：北京·大兴
+薪资：3-6万·13薪
+经验要求：3-5年
+学历要求：硕士
+技能标签：机器学习, Python
+工作职责：
+一、算法开发与实现：
+1.新的数学模拟算法开发：熟练应用各种数值方法（如线性代数求解器、优化算法、数值积分、微分方程求解、蒙特卡洛方法、机器学习模型）解决化学计算问题。针对特定化学问题（如分子动力学模拟、量子化学计算、自由能计算、构象搜索、反应路径探索、机器学习势函数开发等），设计新颖且高效的数值算法和计算方法。并形成知识产权专利。
+2.优化现有算法：分析现有AI模型的计算化学方法的性能瓶颈，对其进行改进、加速或并行化处理，提高计算效率和精度。并形成知识产权专利。
+3.编程实现：使用高性能编程语言（如 Python等）将算法实现为可运行的软件模块或库，确保模块化、可复用与可维护性。
+二、参与模型及数据库的开发工作：如数据收集与预处理、机器学习、模型搭建与训练等工作；实践中探索 AI 技术在医药研发中的创新应用，如新药筛选、靶点识别等场景，尝试进行初步的算法设计与实现。保持对前沿技术的敏感与好奇，主动学习行业新知识，培养独立思考与技术创新能力。
+三、团队协作与跨部门沟通：主动参与团队讨论和协作，积极与医药研发、数据科学等不同背景成员协作交流。清晰表达技术思路和问题，逐步建立起 AI 与医药需求之间的有效沟通桥梁。
+四、其他：负责协助领导完成日常临时性的工作以及部门的公共事务。学习了解医药行业相关法律法规，强化数据安全意识，确保模型研发和数据处理过程符合合规要求以及数据保护。
+任职要求：
+1.教育背景：具有计算生物学、生物信息学、化学信息学、量子化学、人工智能学等硕士及以上学历，具有海外经验优先。
+2.工作经验：AI大模型算力算法工作经验，具有大型药企工作经验优先。
+3.有团队的能力，做过小分子或多肽药物设计算法的优先。</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>算法工程师</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>["AI模型", "Python", "优化", "分子动力学模拟", "反应路径探索", "并行化", "微分方程求解", "数值方法", "数值积分", "数据收集", "机器学习", "机器学习势函数", "构象搜索", "模型搭建", "线性代数求解器", "自由能计算", "蒙特卡洛方法", "量子化学计算"]</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>{"min_years": 3, "max_years": 5}</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>硕士</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>["数值算法开发与优化", "AI 模型与数据库开发", "医药研发 AI 创新应用探索", "团队协作与跨部门沟通"]</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>AI-ZCode</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>r3_003</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>zhilian</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CCL1521769630J40881816609</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>http://www.zhaopin.com/jobdetail/CCL1521769630J40881816609.htm</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>高级java后端工程师</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>北京颢辰科创科技有限公司</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>岗位名称：高级java后端工程师
+公司：北京颢辰科创科技有限公司
+工作地点：北京·海淀·北下关
+薪资：1.5-2万
+经验要求：5-10年
+学历要求：本科
+技能标签：Java, 多线程, Mybatis, MySQL, Redis, MongoDB, Spring, Hadoop
+岗位职责:
+1、气象业务系统开发：负责气象核心业务系统的后端架构设计与开发（包括气象数据采集、处理、存储、服务发布及预报预警平台）。
+2、GIS空间数据处理：基于空间数据库和GIS技术，处理和管理气象站点、雷达回波、卫星云图、行政区划等地理空间数据，提供空间查询与分析服务。
+3、海量数据处理：处理各类气象数据（包括地面/高空观测、雷达、卫星、数值预报模式数据），实现数据的解析、存储、检索与分发。
+4、API服务开发：设计并开发高并发、低延迟的RESTful API接口，支撑前端可视化平台及第三方气象服务调用。
+5、性能优化：针对气象数据量大、计算复杂的特性，进行数据库优化、查询性能优化及系统架构调优。
+任职要求:
+1、基础要求：
+1）学历专业：本科及以上学历，计算机、地理信息、大气科学、数学或相关专业。
+2）Java功底：5年以上Java开发经验，扎实的Java基础，精通多线程、IO、集合框架及JVM调优；熟悉Spring Boot、Spring Cloud、MyBatis等主流框架。
+3）GIS开发经验：熟悉空间数据处理技术，熟练使用PostGIS（PostgreSQL）、MySQL Spatial或Oracle Spatial等空间数据库；熟悉GeoServer、GeoWebCache等地图服务技术者优先。
+4）行业背景：有气象、环保、海洋、航天或地理信息行业项目经验者优先；理解气象常用数据格式（如GRIB、NetCDF、HDF5、BUFR、Micaps）者优先。
+5）数据库能力：精通关系型数据库（MySQL/PostgreSQL）及非关系型数据库（Redis、MongoDB、InfluxDB/TDengine时序数据库），具备海量数据存储与优化经验。
+6）空间分析能力：熟悉空间索引原理，掌握空间查询、缓冲区分析、叠加分析等GIS空间算法
+7）数据格式解析
+8）消息中间件
+9）容器化</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Java后端开发工程师</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>["GIS", "GeoServer", "GeoWebCache", "Hadoop", "IO", "InfluxDB", "JVM调优", "Java", "MongoDB", "MyBatis", "MySQL", "MySQL Spatial", "Oracle Spatial", "PostGIS", "PostgreSQL", "RESTful API", "Redis", "Spring Boot", "Spring Cloud", "TDengine", "叠加分析", "多线程", "容器化", "数据格式解析", "消息", "空间查询", "空间索引", "缓冲区分析", "集合", "集合框架"]</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>["GeoServer", "GeoWebCache", "GRIB", "NetCDF", "HDF5", "BUFR", "Micaps"]</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>{"min_years": 5, "max_years": 10}</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>本科</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>["气象业务系统后端架构设计与开发", "GIS 空间数据处理与管理", "海量气象数据解析存储检索", "RESTful API 服务开发与性能优化"]</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>AI-ZCode</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>r3_004</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>zhilian</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CCL1241548470J40928663912</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>http://www.zhaopin.com/jobdetail/CCL1241548470J40928663912.htm</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>前端工程师（兼美工）</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>上海新炬网络信息技术股份有限公司</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>岗位名称：前端工程师（兼美工）
+公司：上海新炬网络信息技术股份有限公司
+工作地点：广州·天河·冼村
+薪资：1-1.3万·13薪
+经验要求：1-3年
+学历要求：本科
+技能标签：Vue, React, Echarts, VIBECODING, UI, 大屏可视化, ElementUI
+岗位职责：
+1、负责运维平台的前端功能开发，基于 JSP、Vue、React 技术栈完成页面与交互实现；
+2、承担页面美工与 UI 优化工作，负责产品的前端界面优化、体验改进等工作，保障界面视觉效果与用户体验一致性；
+3、根据产品需求进行原型设计，负责公司产品前端功能模块的设计、规划及开发工作;
+4、对接后端服务接口，完成前后端联调，配合测试团队完成功能验证；
+5、沉淀前端开发与可视化设计相关文档，持续优化前端工程化方案；
+6、借助 VibeCoding 等 AI 工具提升开发效率，落地前端智能化开发流程；
+任职要求：
+1、本科及以上学历，计算机、设计相关专业优先；
+2、两年及以上前端开发工作经验，有运维平台开发经验优先；
+3、具备扎实的美工基础，可独立完成页面 UI 设计与视觉优化；
+4、熟练掌握 JSP、Vue 技术栈，熟悉 React 框架开发；
+5、精通 Echarts 等可视化组件，可独立完成大屏数据可视化设计与开发；
+6、有 VibeCoding 等 AI 编码工具使用经验，可借助 AI 提升开发效率；
+7、熟悉前端工程化工具，掌握前后端接口联调流程；
+加分技术能力：
+1、有运维管理平台、监控平台类项目开发经验；
+2、熟悉 Docker、K8s 环境下的前端部署流程；
+3、了解前端性能优化与安全加固方案；
+4、具备设计工具（如 Figma、PS）使用能力；
+综合素质：
+1、具备良好的审美能力与交互设计思维，关注用户体验；
+2、学习能力强，可快速掌握新的可视化技术与 AI 工具；
+3、沟通协作顺畅，可对接产品、后端、测试多角色推进需求落地；
+4、工作细致，具备规范的文档编写习惯。</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>前端开发工程师</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>["ECharts", "Echarts", "ElementUI", "JSP", "React", "UI设计", "VibeCoding", "Vue", "Vue.js", "前端工程化", "原型", "大屏可视化", "数据可视化"]</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>["Docker", "Kubernetes", "前端性能优化", "Figma", "Photoshop"]</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>{"min_years": 1, "max_years": 3}</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>本科</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>["运维平台前端功能开发", "页面美工与 UI 优化", "原型设计与功能模块开发", "前后端接口联调"]</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>AI-ZCode</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>r3_005</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>zhilian</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CC383625320J40877418409</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>http://www.zhaopin.com/jobdetail/CC383625320J40877418409.htm</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>cka销售策略运营专家</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>北京三快在线科技有限公司</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>岗位名称：cka销售策略运营专家
+公司：北京三快在线科技有限公司
+工作地点：北京
+薪资：面议
+经验要求：3-5年
+学历要求：本科
+技能标签：
+快驴进货是美团旗下的餐饮供应链平台，帮助餐饮商户以更低成本、更高效率来获取安全可靠的食材供应，让餐饮采购更简单。快驴进货同步发展“自营+平台”的业务模式，在采购环节一方面向上游供应商直采大宗商品，另一方面引入各地批发商，助力平台伙伴共同发展；在销售环节既有自建团队进行市场、客户拓展，又帮助各地批发商拓展业务；同时自建仓储管理系统、配送网络与团队，为客户提供优质履约服务。
+截至2022年，快驴进货布局了全国41个城市，为百万家商户提供“全、省、稳、好”的餐饮供应链服务。我们拥有3000+品牌食材、超5万SKU商品、超28万商品资质，并提供源头严审核、食品安全严把关、24小时无忧售后的全面保障，实现手机下单、送货上门的高效采购模式，帮百万商家节省了采购时间与成本，助力平台伙伴共同发展，在万亿市场共享机遇。
+在这里，你将收获完善的员工发展机制及学习体系，与各界专家一起深度参与餐饮供应链业务的发展。欢迎优秀的你加入美团快驴进货，与我们一起成长，一起更好！
+岗位职责
+1. 负责制定并优化cka销售策略，提升销售团队整体业绩表现。
+2. 分析市场趋势与客户需求，为销售策略提供数据支持和决策依据。
+3. 协同产品、市场及运营团队，推动销售策略落地并持续迭代。
+4. 建立销售流程标准与评估体系，提升销售效率与团队执行力。
+5. 定期输出销售策略分析报告，向管理层汇报关键指标与改进建议。
+岗位基本需求
+1. 大学本科及以上学历，市场营销、商业管理或相关专业优先。
+2. 5年以上销售运营或销售策略相关工作经验，具备互联网或科技行业背景。
+3. 熟悉销售流程管理，具备较强的数据分析与策略规划能力。
+4. 优秀的沟通协调能力，能够跨部门推动项目落地。
+5. 具备敏锐的市场洞察力与商业敏感度，结果导向。
+岗位亮点
+1. 参与核心销售策略制定，直接影响业务增长方向。
+2. 与行业精英团队共事，获得快速成长与专业能力提升。
+3. 工作地点位于北京核心商务区，办公环境优越。
+4. 提供具有竞争力的薪酬与完善的职业发展通道。</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>销售策略运营专家</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>["市场分析", "数据分析", "策略规划", "销售策略"]</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>{"min_years": 5, "max_years": null}</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>本科</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>["销售策略制定与优化", "市场趋势与客户需求分析", "跨部门协同推进策略落地", "销售流程标准与评估体系建设"]</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>AI-ZCode</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>r3_006</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>zhilian</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CC337626410J40874016110</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>http://www.zhaopin.com/jobdetail/CC337626410J40874016110.htm?refcode=4019&amp;srccode=401903&amp;preactionid=ebb73924-53fd-4947-a040-069e059123ec</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Java开发（文旅电商，3年以上经验）</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>北京青钱信息技术有限公司</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>岗位名称：Java开发（文旅电商，3年以上经验）
+公司：北京青钱信息技术有限公司
+工作地点：北京·朝阳·朝外
+薪资：1.3-1.5万
+经验要求：3-5年
+学历要求：本科
+技能标签：Spring, MySQL
+短期3-6个月；做过文旅和电商，有文旅领域开发经验优先；提供三餐；线上面试
+岗位职责：
+设计和开发高性能、高可用的电商后端系统，包括订单、商品、用户、支付等核心模块；
+负责复杂业务场景下的多接口调用与数据处理，优化调用链路和接口性能；
+对接第三方服务（支付、物流、短信等），确保接口调用的稳定性和数据一致性；
+参与系统架构设计、微服务拆分及优化，提升系统扩展性和可维护性；
+分析并解决生产环境中的技术问题，保障系统的稳定运行；
+编写技术文档，制定开发规范，提升团队的技术能力。
+任职要求：
+1.统本及以上学历，计算机相关专业，3年以上后端开发经验，要求做过文旅和电商，有文旅领域开发经验优先；
+2.熟练掌握至少一种后端开发语言（如Java、Go、Python等），有Spring Boot、Spring Cloud或类似框架的实际经验；
+3.深入理解RESTful API设计，熟悉接口文档编写工具（如Swagger、Postman等）；
+4.熟悉常见的数据库（如MySQL、PostgreSQL）及缓存技术（如Redis）；
+5.具备复杂系统中多服务、多接口调用的经验，能够优化接口性能和调用效率；
+6.有微服务架构经验，熟悉容器化（如Docker、Kubernetes）部署；
+7.熟悉分布式系统的设计和开发，了解分布式事务、CAP理论、负载均衡等相关技术；
+8.对常用第三方接口（支付、物流、短信等）的对接和调优有实战经验；
+9.熟悉常见的消息队列（如RabbitMQ、Kafka）及其在高并发场景下的使用；
+10.具备较强的问题定位和解决能力，对性能调优有深入了解；
+11.良好的沟通能力和团队协作精神，能承受一定的工作压力。</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Java开发工程师</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>["Apache Kafka", "CAP理论", "Docker", "Go", "Java", "Kafka", "Kubernetes", "MySQL", "PostgreSQL", "Postman", "Python", "RESTful API", "RabbitMQ", "Redis", "Spring Boot", "Spring Cloud", "Swagger", "分布式", "分布式事务", "分布式系统", "微服务", "性能调优", "负载均衡"]</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>{"min_years": 3, "max_years": 5}</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>本科</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>["电商后端系统设计与开发", "多接口调用与性能优化", "第三方服务对接", "微服务拆分与架构优化"]</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>AI-ZCode</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>r3_007</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>zhilian</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>CC623052130J40898809112</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>http://www.zhaopin.com/jobdetail/CC623052130J40898809112.htm</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AI 大模型项目经理（油气方向）</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>北京昊锐科技有限公司</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>岗位名称：AI 大模型项目经理（油气方向）
+公司：北京昊锐科技有限公司
+工作地点：北京·海淀·上地
+薪资：2.5-5万
+经验要求：5-10年
+学历要求：本科
+技能标签：AI项目, PMP
+一、 岗位定位
+您将主导油气行业高标准的私有大模型（10B/70B/140B）+ 地质 Agent + 向量知识库全流程项目建设和交付。您既是技术专家，也是项目经理，更是客户信任的 “定海神针”。
+二、 岗位职责
+1. 项目全生命周期掌舵
+1) 独立负责10B（试点）、70B（主力）、140B（高端）三档私有大模型及地质 Agent 项目的售前、立项、实施、验收、运维全流程管理。
+2) 制定项目 WBS（工作分解结构）、里程碑计划与预算，精准控制项目的成本、进度与质量。
+2. 方案与售前攻坚
+1) 独立编制私有大模型部署方案、向量知识库建设方案、Agent 功能方案，并向油田客户高层进行技术宣讲与汇报。
+2) 深度挖掘客户需求，结合涉密合规要求，输出方案对比建议，支撑商务报价与投标。
+3. 技术落地与统筹
+1) 统筹、协调算法、开发、硬件、地质专家团队，推动以下关键技术节点的落地交付：
+(1) GPU 服务器选型与部署：L40S/H100/Atlas 910B/950等显卡服务器选型、K8s/Docker 容器化部署。
+(2) 模型管理：开源模型（Llama/Qwen/DeepSeek等）微调、推理加速、多版本管理。
+(3) 数据治理：油气地质数据脱敏、分级分类、向量知识库构建与检索优化。
+(4) Agent 开发：RAG 检索增强、工具调用（对接 FLAC3D/CMG/ECLIPSE）、报告生成。
+(5) 安全合规：内网物理隔离、堡垒机接入、操作审计日志配置。
+4. 涉密合规与风险管控
+严格遵守油田涉密数据管理规范，确保全流程无公网接触、数据不外泄，把控安全合规风险，出具安全合规报告。
+5. 沉淀与标准化
+总结项目交付经验，沉淀标准方案库、实施手册、交付模板，提升多项目复用效率。
+三、
+岗位要求
+1. 本科及以上学历，计算机、人工智能、软件工程、石油工程、地质工程等相关专业优先。
+2. 5年及以上IT / 数字化项目管理经验。其中2年及以上油气 / 能源行业 AI / 数字化项目经验；至少 1 个完整的私有大模型（70B 及以上）落地交付经验，有 140B 集群部署经验者优先考虑。
+3. 精通10B/70B/140B 开源大模型的私有化部署、微调、推理优化流程；精通向量数据库（Milvus/FAISS 等）搭建与 RAG 技术落地，具有油气行业知识库构建经验；有百万级以上 AI 项目独立交付业绩者优先考虑。
+4. 了解GPU 服务器硬件架构，熟悉 K8s/Docker 容器化部署；了解Petrel/FLAC3D/CMG/ECLIPSE等地质 / 油藏软件生态者优先。
+5. 具备跨团队协调能力，不包括但不限于算法团队、硬件团队、地质专家组及客户项目组；抗压能力强，能适应油田项目驻场与艰苦的出差环境；保密意识强。
+6. 结果导向，对数据安全和项目交付质量有极高的责任心，敢于直面各种困难与挑战，确保高质量、高效率交付。
+四、 岗位亮点与待遇
+1. 参与油气行业最前沿的大模型落地，积累垂直行业 AI 交付经验。
+2. 直接接触中石油/中石化等头部客户，拓展高价值行业人脉。
+3. 提供充分的个人职业发展和晋升空间，直至成为公司合伙人。
+4. 工资+分红+五险一金+带薪年假。</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>AI大模型项目经理</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>["Docker", "FAISS", "Kubernetes", "Milvus", "RAG", "向量数据库", "大语言模型", "推理优化", "检索增强生成", "模型微调"]</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>["Petrel", "FLAC3D", "CMG", "ECLIPSE"]</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>{"min_years": 5, "max_years": 10}</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>本科</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>["私有大模型项目全生命周期管理", "大模型部署方案与售前攻坚", "GPU 服务器选型与容器化部署", "模型微调与推理加速管理", "RAG 向量知识库构建"]</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>AI-ZCode</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>r3_008</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>zhilian</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>CCL1522955370J40868278711</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>http://www.zhaopin.com/jobdetail/CCL1522955370J40868278711.htm</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AI 铝合金材料大模型工程师</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>中利科威(苏州)新材料有限公司</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>岗位名称：AI 铝合金材料大模型工程师
+公司：中利科威(苏州)新材料有限公司
+工作地点：苏州
+薪资：1.5-3万
+经验要求：3-5年
+学历要求：硕士
+技能标签：大模型算法
+1. AI材料智能体技术战略与产品路线
+作为项目第一技术责任人，制定 AI材料智能体中长期技术战略、产品架构和阶段性里程碑；明确 MVP、工程版、平台化产品的演进路径。围绕材料研发、轻量化减薄、力学仿真、工艺优化、知识问答、报告生成等高价值场景，确定优先级并推动形成可落地产品。
+2. 总体技术架构与关键技术决策
+全权负责技术体系顶层设计与关键技术选型，构建“大模型/多模态模型 + RAG/知识图谱 + Agent编排 + 专业材料模型 + 仿真工具链 + 企业数据平台”的统一架构。负责模型服务、工具调用、工作流编排、权限、安全、评测、部署和扩展性等核心能力，解决系统瓶颈与架构债务。
+3. 材料数据底座与知识工程
+牵头建立材料领域数据标准与数据资产体系，打通“成分—组织—工艺—性能—仿真—实验—生产”全链条数据；统筹结构化数据、实验记录、技术文档、图纸/三维模型、CAE结果、工艺参数等多源数据治理，建立可追溯、可持续迭代的数据闭环，为智能体训练、检索、推理与评测提供统一底座。
+4. 核心智能体与专业模型研发
+带领团队研发材料知识智能体、减薄优化智能体、力学/CAE仿真智能体、材料配方与工艺智能体等核心模块。推动 LLM/VLM、RAG、知识图谱、PINN/GNN、代理模型、优化算法等技术与材料机理深度融合，建立准确性、稳定性、时延、可解释性和工程可用性指标体系。
+5. 仿真与工程软件工具链集成
+推动智能体与 CAD/CAE/有限元、材料数据库、实验分析及企业内部软件系统打通，实现模型可调用工具、自动拆解任务、生成分析方案、驱动仿真计算、读取结果并给出工程建议。重点建立“AI提出方案—仿真验证—结果反馈—模型迭代”的闭环。
+6. 产品化、工程化与客户交付
+对技术成果从 Demo、POC 到正式产品交付负责。推动私有化部署、推理优化、接口服务、权限审计、稳定性、数据安全和运维体系建设；与产品、材料研发、工艺、仿真、销售及客户团队协同，定义验收标准和业务价值指标，确保产品真正解决研发效率、试验成本、轻量化设计和工程决策问题。
+7. 技术团队搭建与组织管理
+负责 AI材料智能体技术团队的组织设计、人才招聘、培养和绩效管理，逐步搭建算法/大模型、材料数据、CAE/仿真、后端平台与工程化等核心能力。建立技术评审、代码规范、模型评测、研发流程、项目节奏与复盘机制，形成可持续交付的技术组织。
+8. 跨部门协同与技术价值转化
+联动材料、研发、工艺、生产、销售和管理层，将业务问题转化为 AI 可解决的问题，并把技术成果转化为可量化的降本、提效、减重、缩短研发周期和提升决策质量。参与重大客户技术交流、方案评审、项目攻关与关键交付。
+9. 外部生态、知识产权与技术影响力
+统筹高校、科研院所、算力/模型厂商、工业软件与产业合作伙伴等外部资源；推动专利、软著、技术标准、科研项目和产学研合作，建立公司在“AI + 材料智能研发”方向的技术壁垒与行业影响力。
+三、
+任职要求
+1. 经验与角色要求
+8年以上 AI、工业软件、材料数字化、科学智能或相关领域经验，3年以上技术负责人/架构负责人/研发负责人经历；有从0到1带领团队做成 AI/工业软件产品并完成真实业务落地的经验。特别优秀者可不受年限和学历限制。
+2. AI与系统架构能力
+熟悉主流大模型、RAG、Agent、多模态、模型微调/对齐、推理优化、知识图谱、向量检索及企业级部署；具备复杂 AI系统架构设计能力，能对模型、数据、平台、工具链和工程部署做整体权衡，而不是只聚焦单一算法。
+3. 材料/仿真理解能力
+理解材料研发基本逻辑，能够与材料专家、仿真工程师和工艺工程师高效沟通；熟悉“成分—组织—工艺—性能”关系、压铸/铝合金研发流程、材料测试或 CAE/有限元仿真者优先。
+4. 工程落地能力
+具备工业数据治理、模型工程化、私有化部署、API/工具调用、数据安全与系统集成经验；能够亲自参与关键架构设计、技术难点攻关和技术评审，既能带团队，也能在关键阶段下场解决问题。
+5. 管理与商业意识
+具备较强的团队领导、跨部门统筹和对外沟通能力；能够用业务价值衡量技术优先级，以交付结果、客户价值和可复制性为导向，不以“模型指标”或“技术新颖度”作为唯一判断标准。</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>AI大模型工程师</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>["AGENT", "Agent", "CAE", "GNN", "PINN", "RAG", "VLM", "优化", "向量检索", "多模态模型", "大语言模型", "推理优化", "数据治理", "有限元仿真", "检索增强生成", "模型对齐", "模型微调", "知识图谱"]</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>["CAE仿真", "有限元分析"]</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>{"min_years": 8, "max_years": null}</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>硕士</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>["AI 材料智能体技术战略规划", "材料数据底座与知识工程", "智能体与专业模型研发", "CAE 仿真工具链集成", "私有化部署与产品交付"]</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>AI-ZCode</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>r3_010</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>linkedin_public</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>li-4454056326</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4454056326</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>SDET with Python &amp; AI</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>MPower Plus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>{"id": "li-4454056326", "site": "linkedin", "job_url": "https://www.linkedin.com/jobs/view/4454056326", "job_url_direct": "", "title": "SDET with Python &amp; AI", "company": "MPower Plus", "location": "Sunnyvale, CA", "date_posted": "2026-08-13", "job_type": "fulltime", "salary_source": "", "interval": "", "min_amount": "", "max_amount": "", "currency": "", "is_remote": false, "job_level": "mid-senior level", "job_function": "", "listing_type": "", "emails": "", "description": "**Role: SDET with Python \\&amp; AI** \n\n\n\n\n**Location: Sunnyvale, CA** \n\n\n\n\n**Job Type: FTE and W2 Contract** \n\n\n\n\n  \n\n\n\n\n\n**SDET with Python coding, AI, Selenium is must or look for AI Engineer with Python coding and rest JD sam** \n\n\n\n\n  \n\n\n\n\n\n e\n   \n\n Ex Apple is always welco\n \n\n\n\n  \n\n\n\n\n\n**me\n   \n\n Need hands on Python co** \n\n\n\n\n  \n\n\n\n\n\n**der\n   \n\n Must Have Ski**\n\n\n\n\n**lls:⦁ Selenium Automation with Java and pyt** \n\n\n\n\n**hon Python coding is must, JAVA is secon** \n\n\n\n\n**daryKnowledge on utilizing Ai tools for automation must and usage needs to justified \\- tools Microsoft copilot/ Claude/ curs** \n\n\n\n\n  \n\n\n\n\n\n**or.\n   \n\n ⦁ API Automa** \n\n\n\n\n**tion ⦁ BDD/Cuc** \n\n\n\n\n**umber⦁ CI/CD integr** \n\n\n\n\n  \n\n\n\n\n ation", "company_industry": "IT Services and IT Consulting", "company_url": "https://uk.linkedin.com/company/mpowerplus", "company_logo": "https://media.licdn.com/dms/image/v2/D4E0BAQHk1Oo0GvY9yQ/company-logo_100_100/B4EZ1n1.XaGYAQ-/0/1775563696163/mpowerplus_logo?e=2147483647&amp;v=beta&amp;t=qnPCW4RicuQsZzIgknv5FtZ0zNCr5E1bqCwQI6dgsV0", "company_url_direct": "", "company_addresses": "", "company_num_employees": "", "company_revenue": "", "company_description": "", "skills": "", "experience_range": "", "company_rating": "", "company_reviews_count": "", "vacancy_count": "", "work_from_home_type": ""}</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>测试开发工程师</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>["AI", "BDD", "CI/CD", "Claude", "Cucumber", "Cursor", "Java", "Microsoft Copilot", "Python", "Selenium", "接口自动化测试"]</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>["Python 自动化测试开发", "AI 工具辅助自动化", "API 自动化测试", "BDD/Cucumber 测试集成"]</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>AI-ZCode</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>r3_011</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>linkedin_public</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>li-4454096021</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4454096021</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Thatcher</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>GSOBA</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>{"id": "li-4454096021", "site": "linkedin", "job_url": "https://www.linkedin.com/jobs/view/4454096021", "job_url_direct": "", "title": "Thatcher", "company": "GSOBA", "location": "San Francisco, CA", "date_posted": "2026-08-13", "job_type": "fulltime", "salary_source": "", "interval": "", "min_amount": "", "max_amount": "", "currency": "", "is_remote": false, "job_level": "director", "job_function": "Engineering and Information Technology", "listing_type": "", "emails": "", "description": "Thatch and re\\-ridge cottage and barn roofs with water reed and combed wheat, fixing courses to the rafters, dressing the coatwork with a leggett, and shaping decorative ridges that shed rain for decades. You will work at height in the open, strip worn thatch, manage materials on site, and quote heritage jobs directly for owners. A head for heights, real physical stamina, and a thatching apprenticeship are required for this role.", "company_industry": "Technology, Information and Internet and IT Services and IT Consulting", "company_url": "https://cn.linkedin.com/company/gsobatestpage1", "company_logo": "https://media.licdn.com/dms/image/v2/C4E0BAQEQTydUvwmcag/company-logo_100_100/company-logo_100_100/0/1630579932293?e=2147483647&amp;v=beta&amp;t=WoLxhaIy15Kn4EXqCbsk0LmN-mVhH0gt8mFO8WVw2HY", "company_url_direct": "", "company_addresses": "", "company_num_employees": "", "company_revenue": "", "company_description": "", "skills": "", "experience_range": "", "company_rating": "", "company_reviews_count": "", "vacancy_count": "", "work_from_home_type": ""}</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Thatcher</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>["茅草屋顶修缮与铺设", "高处作业与材料管理", "遗产项目报价"]</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>AI-ZCode</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>r3_012</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>linkedin_public</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>li-4454079879</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4454079879</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Haystack</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>{"id": "li-4454079879", "site": "linkedin", "job_url": "https://www.linkedin.com/jobs/view/4454079879", "job_url_direct": "", "title": "Senior Data Engineer", "company": "Haystack", "location": "New York, NY", "date_posted": "2026-08-13", "job_type": "fulltime", "salary_source": "", "interval": "", "min_amount": "", "max_amount": "", "currency": "", "is_remote": false, "job_level": "mid-senior level", "job_function": "Information Technology", "listing_type": "", "emails": "", "description": "We're working with a leading consulting firm that specializes in digital transformation and innovative technology solutions, driving significant impact for their clients across various industries.\n   \n\n  \n\n The Role\n   \n\n  \n\n* Design, develop, and maintain robust data pipelines and infrastructure\n* Lead the migration of on\\-premises data systems to cloud platforms\n* Optimize and transform large datasets using advanced data engineering techniques\n* Implement and ensure data quality, governance, and security standards\n* Collaborate with cross\\-functional teams to deliver scalable data solutions\n* Mentor junior data engineers and contribute to best practices\n\n\n What You'll Need\n   \n\n  \n\n* Minimum 5\\-7 years of data engineering experience with 3\\+ years in Databricks production environments\n* Proven expertise in migrating data systems to cloud platforms (preferably Azure)\n* Strong proficiency in Python, PySpark, and SQL; experience with Spark SQL transformations\n* Familiarity with CI/CD, data quality frameworks, and orchestration tools like Airflow or dbt\n* Experience with large\\-scale data modernization programs is a plus\n* Strong problem\\-solving, communication, and stakeholder management skills\n\n\n What's On Offer\n   \n\n  \n\n* Opportunity to work on cutting\\-edge data migration and modernization projects\n* Collaborative and innovative work environment with a focus on professional growth\n* Exposure to diverse industries, including financial services\n* Competitive compensation package and benefits\n\n\n Apply via Haystack today!", "company_industry": "Technology, Information and Internet", "company_url": "https://uk.linkedin.com/company/wearehaystack", "company_logo": "https://media.licdn.com/dms/image/v2/D4E0BAQFq9pcJGgSIpw/company-logo_100_100/company-logo_100_100/0/1661435358398/wearehaystack_logo?e=2147483647&amp;v=beta&amp;t=rujfUADbjJfzHP5KvyRjFwVpiCqcmuXrLF36sSaB1m8", "company_url_direct": "", "company_addresses": "", "company_num_employees": "", "company_revenue": "", "company_description": "", "skills": "", "experience_range": "", "company_rating": "", "company_reviews_count": "", "vacancy_count": "", "work_from_home_type": ""}</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>数据工程师</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>["Databricks", "Python", "PySpark", "SQL", "Spark SQL", "CI/CD", "Airflow", "dbt"]</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>["Azure"]</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>{"min_years": 5, "max_years": 7}</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>["数据管道设计与维护", "本地系统迁移上云", "大数据集优化与转换", "数据质量治理与安全"]</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>AI-ZCode</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>r3_013</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>linkedin_public</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>li-4444004139</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4444004139</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Houseperson - Housepersona</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>The Unbound Collection by Hyatt</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>{"id": "li-4444004139", "site": "linkedin", "job_url": "https://www.linkedin.com/jobs/view/4444004139", "job_url_direct": "", "title": "Houseperson - Housepersona", "company": "The Unbound Collection by Hyatt", "location": "York, NY", "date_posted": "2026-08-14", "job_type": "fulltime", "salary_source": "", "interval": "", "min_amount": "", "max_amount": "", "currency": "", "is_remote": false, "job_level": "entry level", "job_function": "Management and Manufacturing", "listing_type": "", "emails": "", "description": "**Organization\\- The Chatwal**\n**Resumen**\n El empleado de Housekeeping es responsable de mantener limpio el hotel. Esta persona tiene que tener buenos conocimientos de comunicación y también la habilidad de levantar, tirar y empujar peso moderado. En este puesto se trabaja a un ritmo muy rápido.", "company_industry": "Hospitality", "company_url": "https://www.linkedin.com/company/the-unbound-collection-by-hyatt", "company_logo": "https://media.licdn.com/dms/image/v2/C560BAQH6vua5UhSLGg/company-logo_100_100/company-logo_100_100/0/1657141088257/the_unbound_collection_by_hyatt_logo?e=2147483647&amp;v=beta&amp;t=SxnYjWimTU9vtMGGTRVCnAcOz83H9XfJrIgmjynTaEU", "company_url_direct": "", "company_addresses": "", "company_num_employees": "", "company_revenue": "", "company_description": "", "skills": "", "experience_range": "", "company_rating": "", "company_reviews_count": "", "vacancy_count": "", "work_from_home_type": ""}</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>客房服务员</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>["酒店客房清洁维护", "物品搬运与整理", "快速节奏工作"]</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>AI-ZCode</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>r3_014</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>linkedin_public</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>li-4450442917</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4450442917</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>WEB前端开发</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>ZTCcloud</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>{"id": "li-4450442917", "site": "linkedin", "job_url": "https://www.linkedin.com/jobs/view/4450442917", "job_url_direct": "", "title": "WEB前端开发", "company": "ZTCcloud", "location": "Changsha, Hunan, China", "date_posted": "2026-08-13", "job_type": "fulltime", "salary_source": "", "interval": "", "min_amount": "", "max_amount": "", "currency": "", "is_remote": false, "job_level": "entry level", "job_function": "Engineering and Information Technology", "listing_type": "", "emails": "", "description": "该职位来源于猎聘 数智化前端研发工程师 您将参与公司数智化产品在 H5、web 端和移动端的开发与维护工作，同时勇挑新产品 H5 前端开发或小程序开发重任。与后端团队紧密协作，攻克前端难题，封装并优化常用前端组件及工具库，持续完善前端技术规范。 岗位要求 1、本科及以上学历,计算机相关专业优先； 2、精通HTML5、CSS3、Vue.js 及 SASS，熟悉页面架构和布局； 3、了解原生JavaScript原理，熟悉 ES5/ES6 特性，理解函数式与面向对象编程思想，有TypeScript 使用经验优先； 4、有使用过Angular.js、React 经验优先; 5、熟悉GIT代码管理工具，具备优秀的代码编写能力; 6、熟悉Echarts，能够熟练运用进行数据可视化开发； 7、掌握3D模技术，了解虚拟现实相关技术，有相关项目经验者优先。", "company_industry": "Technology, Information and Internet", "company_url": "https://cn.linkedin.com/company/ztccloud", "company_logo": "https://media.licdn.com/dms/image/v2/C510BAQGfYOYe7j0eiA/company-logo_100_100/company-logo_100_100/0/1630621936974?e=2147483647&amp;v=beta&amp;t=5mc1B8I0r-43NUZWAig4UpbrjRrfYWEGVaggRlZheXI", "company_url_direct": "", "company_addresses": "", "company_num_employees": "", "company_revenue": "", "company_description": "", "skills": "", "experience_range": "", "company_rating": "", "company_reviews_count": "", "vacancy_count": "", "work_from_home_type": ""}</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>前端开发工程师</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>["3D建模", "CSS3", "ECharts", "ES5", "ES6", "Echarts", "Git", "HTML5", "JavaScript", "SASS", "Sass", "TypeScript", "Vue.js", "小程序", "小程序开发", "数据可视化", "虚拟现实"]</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>["TypeScript", "AngularJS", "React"]</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>本科</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>["H5/Web/移动端开发维护", "前端组件封装与优化", "数据可视化开发", "3D 与虚拟现实技术探索"]</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>AI-ZCode</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>r3_015</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>linkedin_public</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>li-4453517479</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4453517479</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Frontend Developer</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Kaizen Global Technologies</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>{"id": "li-4453517479", "site": "linkedin", "job_url": "https://www.linkedin.com/jobs/view/4453517479", "job_url_direct": "", "title": "Frontend Developer", "company": "Kaizen Global Technologies", "location": "Sydney, New South Wales, Australia", "date_posted": "2026-08-14", "job_type": "fulltime", "salary_source": "", "interval": "", "min_amount": "", "max_amount": "", "currency": "", "is_remote": false, "job_level": "mid-senior level", "job_function": "Information Technology", "listing_type": "", "emails": "[EMAIL]", "description": "**Location:** \n Sydney, Australia\n \n\n\n\n**Experience:** \n 7\\+ Years\n \n\n\n\n**Employment Type:** \n Permanent\n \n\n\n\n**Eligibility:** \n Candidates must have full working rights in Australia (Citizen, PR, or Valid Visa holders).\n \n\n\n\n  \n\n\n\n\n\n Key Responsibilities\n \n\n\n* Develop responsive, scalable, and high\\-performance web applications using\n **React.js, Next.js, TypeScript, and JavaScript** \n .\n* Build reusable UI components and integrate applications with\n **REST APIs and backend services** \n .\n* Develop and maintain automated tests using\n **Playwright, Jest, Cypress, or similar frameworks** \n .\n* Work with\n **Git/GitHub, CI/CD pipelines, and Agile delivery practices** \n to deliver quality software.\n* Collaborate with backend developers, designers, testers, and stakeholders to deliver end\\-to\\-end solutions.\n* Deploy and support applications in\n **AWS cloud environments** \n .\n\n\n\n  \n\n\n\n\n\n Required Skills\n \n\n\n* software development experience with strong front\\-end expertise.\n* Strong hands\\-on experience with\n **React.js, Next.js, TypeScript, and JavaScript** \n .\n* Good knowledge of\n **HTML5, CSS3, responsive design, and modern UI development** \n .\n* Experience integrating\n **REST APIs** \n and working with Git/GitHub.\n* Hands\\-on experience with\n **Playwright, Jest, Cypress, or similar testing frameworks** \n .\n* Understanding of\n **CI/CD, Agile methodologies, and AWS cloud platforms** \n .\n* **Java and Python** \n is desirable.\n\n\n\n  \n\n\n\n\n\n Please drop your CV to [EMAIL]", "company_industry": "IT Services and IT Consulting", "company_url": "https://au.linkedin.com/company/kaizen-global-technologies", "company_logo": "https://media.licdn.com/dms/image/v2/D560BAQGMB_0R2rRKtg/company-logo_100_100/company-logo_100_100/0/1691985782239/kaizen_global_technologies_logo?e=2147483647&amp;v=beta&amp;t=RvS8TaNWbE7L2iER7l7ByNc6K_yz06DI9enChoe_BtA", "company_url_direct": "", "company_addresses": "", "company_num_employees": "", "company_revenue": "", "company_description": "", "skills": "", "experience_range": "", "company_rating": "", "company_reviews_count": "", "vacancy_count": "", "work_from_home_type": ""}</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>前端开发工程师</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>["AWS", "CI/CD", "CSS3", "Cypress", "Git", "GitHub", "HTML5", "JavaScript", "Jest", "Next.js", "Playwright", "RESTful API", "React", "React.js", "TypeScript"]</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>{"min_years": 7, "max_years": null}</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>["响应式 Web 应用开发", "UI 组件库构建与 API 集成", "自动化测试开发维护", "AWS 云环境部署支持"]</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>AI-ZCode</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>r3_016</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>linkedin_public</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>li-4451702050</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4451702050</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>前端开发</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>北京名将教育科技有限公司</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>{"id": "li-4451702050", "site": "linkedin", "job_url": "https://www.linkedin.com/jobs/view/4451702050", "job_url_direct": "", "title": "前端开发", "company": "北京名将教育科技有限公司", "location": "Tianjin, Tianjin, China", "date_posted": "", "job_type": "fulltime", "salary_source": "", "interval": "", "min_amount": "", "max_amount": "", "currency": "", "is_remote": false, "job_level": "entry level", "job_function": "Engineering and Information Technology", "listing_type": "", "emails": "", "description": "该职位来源于猎聘 岗位职责： 1\\.参与并主要负责公司项目和产品的HTML5页面开发与功能实现； 2\\.配合产品经理和UI设计师，对功能型页面程序提供与整合； 3\\.负责前端静态页面及页面JS效果输出； 4\\.应用JavaScript和相关技术与后台进行交互通信； 5\\.负责持续优化网站的用户体验和可用性； 6\\.追踪前端技术的发展，结合实际应用需求进行技术的改进与创新； 职位要求： 1\\.本科及以上学历，熟悉了解HTML5技术； 2\\.熟悉掌握Javascript、HTML/HTML5/XML、CSS3\\.Ajax等前端开发技术； 3\\.熟悉wibkit、手机浏览器适配和基于系统webview的浏览器相关优先； 4\\.有JQueryMobile,SenchaTouch,iWebkit等框架使用经验者优先； 5\\.熟悉各种常见跨浏览器、跨设备问题，深刻理解Web标准，对可用性、可访问性等相关知识有实际的了解和实践经验。", "company_industry": "IT Services and IT Consulting", "company_url": "https://www.linkedin.com/company/%E5%8C%97%E4%BA%AC%E5%90%8D%E5%B0%86%E6%95%99%E8%82%B2%E7%A7%91%E6%8A%80%E6%9C%89%E9%99%90%E5%85%AC%E5%8F%B8", "company_logo": "https://static.licdn.com/aero-v1/sc/h/aajlclc14rr2scznz5qm2rj9u", "company_url_direct": "", "company_addresses": "", "company_num_employees": "", "company_revenue": "", "company_description": "", "skills": "", "experience_range": "", "company_rating": "", "company_reviews_count": "", "vacancy_count": "", "work_from_home_type": ""}</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>前端开发工程师</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>["AJAX", "Ajax", "CSS3", "HTML", "HTML5", "JavaScript", "XML"]</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>["JQueryMobile", "SenchaTouch", "iWebkit"]</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>本科</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>["HTML5 页面开发与功能实现", "前端静态页面与 JS 效果输出", "前后端交互通信", "用户体验优化"]</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>AI-ZCode</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>r3_017</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>indeed</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>in-579b976608761c49</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=579b976608761c49</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Mobile Engineer</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Vervint</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>{"id": "in-579b976608761c49", "site": "indeed", "job_url": "https://www.indeed.com/viewjob?jk=579b976608761c49", "job_url_direct": "https://vervint.com/who-we-are/careers/?gnk=job&amp;gni=8a78839f9fd3ba8701a0022ef82457e3&amp;gns=Indeed+Free", "title": "Mobile Engineer", "company": "Vervint", "location": "Remote, US", "date_posted": "2026-08-14", "job_type": "contract", "salary_source": "", "interval": "", "min_amount": "", "max_amount": "", "currency": "", "is_remote": true, "job_level": "", "job_function": "", "listing_type": "", "emails": "", "description": "**Mobile Engineer (React Native) \\| Remote \\| 4\\-month contract**  \n\n\nWe are seeking a Mobile Engineer to design, develop, and deliver high\\-quality mobile applications using React Native. You’ll lead technical initiatives, collaborate with clients and cross\\-functional teams, mentor engineers, and contribute throughout the software development lifecycle.  \n\n\n**What You’ll Do**\n* Design and develop scalable mobile applications using React Native.\n* Lead technical decisions, architecture, and project workstreams.\n* Build and optimize high\\-performance iOS and Android applications.\n* Develop native modules using Swift/Objective\\-C and Kotlin/Java as needed.\n* Implement automated testing, CI/CD, deployment, and monitoring.\n* Troubleshoot complex technical issues and optimize application performance.\n* Collaborate with clients, architects, QA, and engineering teams.\n* Conduct code reviews, mentor engineers, and promote development best practices.\n* Create documentation and drive continuous improvement.\n\n  \n\n\n**What You’ll Bring**\n* 5–7\\+ years of professional mobile development experience, including 4\\+ years with React Native and 2\\+ years in a senior/lead role.\n* Strong expertise in React Native, including Fabric, JSI, TurboModules, and Hermes.\n* Experience with native iOS and Android development.\n* Experience with mobile testing tools such as Jest, React Native Testing Library, Detox, or Maestro.\n* Familiarity with AWS, Azure, or GCP and modern DevOps practices.\n* Strong understanding of software architecture, APIs, databases, and cloud technologies.\n* Excellent problem\\-solving, communication, and collaboration skills.\n* Bachelor’s degree in Computer Science, Engineering, or related field, or equivalent experience.", "company_industry": "", "company_url": "https://www.indeed.com/cmp/Vervint", "company_logo": "", "company_url_direct": "", "company_addresses": "", "company_num_employees": "", "company_revenue": "", "company_description": "", "skills": "", "experience_range": "", "company_rating": "", "company_reviews_count": "", "vacancy_count": "", "work_from_home_type": ""}</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>React Native移动开发工程师</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>["AWS", "Android", "Android开发", "Azure", "CI/CD", "Detox", "DevOps", "GCP", "Java", "Jest", "Kotlin", "Maestro", "Objective-C", "React Native", "React Native Testing Library", "Swift", "iOS", "iOS开发", "自动化测试"]</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>{"min_years": 5, "max_years": null}</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>["React Native 移动应用开发", "iOS/Android 高性能应用构建", "原生模块开发", "自动化测试与 CI/CD", "代码审查与技术指导"]</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>AI-ZCode</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>r3_018</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>indeed</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>in-34f68efd572c19c2</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=34f68efd572c19c2</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Test Automation Engineer</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Intellibee Inc</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>{"id": "in-34f68efd572c19c2", "site": "indeed", "job_url": "https://www.indeed.com/viewjob?jk=34f68efd572c19c2", "job_url_direct": "https://intellibee.my.salesforce-sites.com/apps/jobs?id=a0AUU000007olVx2AI", "title": "Test Automation Engineer", "company": "Intellibee Inc", "location": "Hanover, MA, US", "date_posted": "2026-08-10", "job_type": "", "salary_source": "", "interval": "", "min_amount": "", "max_amount": "", "currency": "", "is_remote": false, "job_level": "", "job_function": "", "listing_type": "", "emails": "", "description": "**Job Details:**\n\n**Strong Core Java Fundamentals**\n\n* Excellent command over Collections Exception Handling OOP concepts\n* Ability to write optimize and explain Java programs\n* Should demonstrate logic building and complexity understanding\n* Outdated or theoretical Java experience will be rejected\n\n**UI Automation Daily HandsOn**\n\n* Strong experience in Selenium Java\n* Must be able to form XPath locators independently this is tested\n* Handson experience with UI automation frameworks\n* Playwright experience is highly desirable\n\n**API Automation**\n\n* Handson API automation using REST Assured\n* Ability to automate validate and integrate API tests into frameworks\n\n**Automation Framework Architecture**\n\n  \n\nMust have designed or implemented UIAPI automation frameworks\n\n\nShould clearly explain\n\n* Framework structure\n* Execution strategy\n* CICD integration\n\n **Benefits at IntelliBee**\n\n* **Long\\-Term Stability:** Join us on a multi\\-year opportunities with room to grow.\n* **Comprehensive Health Coverage:** Access quality healthcare benefits to keep you and your family well.\n* **Future Planning:** Enroll in our 401(k) program and invest in your financial security.\n* **GC Assistance:** We support immediate Green Card processing, if required.", "company_industry": "Internet And Software", "company_url": "https://www.indeed.com/cmp/Intellibee-Inc", "company_logo": "https://d2q79iu7y748jz.cloudfront.net/s/_squarelogo/256x256/37b7727e3eb2acd948f6f4f73c2701ba", "company_url_direct": "", "company_addresses": "", "company_num_employees": "", "company_revenue": "", "company_description": "", "skills": "", "experience_range": "", "company_rating": "", "company_reviews_count": "", "vacancy_count": "", "work_from_home_type": ""}</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>自动化测试工程师</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>["CI/CD", "Java", "Playwright", "REST Assured", "Selenium", "XPath", "接口自动化测试", "自动化测试"]</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>["Playwright"]</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>["Java 自动化测试开发", "Selenium UI 自动化", "API 自动化测试", "测试框架架构设计"]</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>AI-ZCode</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>r3_019</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>indeed</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>in-b5f44877ffa881a6</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b5f44877ffa881a6</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Hardware Engineer</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Vaspire Technologies</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>{"id": "in-b5f44877ffa881a6", "site": "indeed", "job_url": "https://www.indeed.com/viewjob?jk=b5f44877ffa881a6", "job_url_direct": "http://www.indeed.com/job/hardware-engineer-b5f44877ffa881a6", "title": "Hardware Engineer", "company": "Vaspire Technologies", "location": "Santa Clara, CA, US", "date_posted": "2026-08-13", "job_type": "fulltime, contract", "salary_source": "direct_data", "interval": "yearly", "min_amount": 100024.0, "max_amount": 120460.0, "currency": "USD", "is_remote": false, "job_level": "", "job_function": "", "listing_type": "", "emails": "", "description": "Key Responsibilities  \n•     Perform first\\-level hardware triage and troubleshooting for PCs and server platforms.  \n•     Design and implement diagnostic tools and scripts for early hardware validation and fault isolation.  \n•     Identify and resolve setup issues and test failures using structured troubleshooting methodologies.  \n•     Develop and maintain test automation using Shell and Python scripting.  \n•     Work with motherboards and GPU platforms in lab environments.  \n•     Work with systems connected by various networking protcols, including Ethernet, NVLink and Infiniband  \n•     Operate in Windows and Linux operating systems for test and debug tasks.  \n•     Collaborate with cross\\-functional teams to support diagnostics, validation, and smooth product transitions in the NPI cycle.  \nRequired Skills \\&amp; Qualifications:  \n•     BS Degree in Electrical Engineering or equivalent.  \n•     Strong scripting skills in Python and Shell.  \n•     Familiarity with Windows and Linux OS environments.  \n•     Working knowledge of hardware protocols: Ethernet, Infiniband, PCIe, USB, HDMI, I2C, SPI.  \n•     Experience with CPUs and GPUs.  \n•     Proficient in using test equipment for diagnostics and validation.  \n•     Strong analytical, troubleshooting, and problem\\-solving skills.  \n•     Excellent communication and teamwork skills.  \n· Linux or scripting experience is a huge plus\n\nPay: $100,024\\.97 \\- $120,460\\.17 per year\n\nBenefits:\n\n* Dental insurance\n* Health insurance\n* Relocation assistance\n* Vision insurance\n\nWork Location: In person", "company_industry": "", "company_url": "https://www.indeed.com/cmp/Vaspire-Technologies", "company_logo": "", "company_url_direct": "", "company_addresses": "", "company_num_employees": "", "company_revenue": "", "company_description": "", "skills": "", "experience_range": "", "company_rating": "", "company_reviews_count": "", "vacancy_count": "", "work_from_home_type": ""}</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>硬件工程师</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>["Ethernet", "GPU", "HDMI", "I2C", "InfiniBand", "Infiniband", "Linux", "NVLink", "PCIe", "Python", "SPI", "Shell", "USB", "Windows", "测试自动化"]</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>本科</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>["硬件故障排查与诊断", "诊断工具与脚本开发", "测试自动化", "网络协议调试", "NPI 产品验证支持"]</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>AI-ZCode</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>r3_020</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>indeed</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>in-8dbee6d902c5d909</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8dbee6d902c5d909</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>.Net Developer</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Pat N Sally Inc</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>{"id": "in-8dbee6d902c5d909", "site": "indeed", "job_url": "https://www.indeed.com/viewjob?jk=8dbee6d902c5d909", "job_url_direct": "http://www.indeed.com/job/net-developer-8dbee6d902c5d909", "title": ".Net Developer", "company": "Pat N Sally Inc", "location": "Albany, NY, US", "date_posted": "2026-08-13", "job_type": "fulltime, contract", "salary_source": "direct_data", "interval": "hourly", "min_amount": 85.0, "max_amount": 90.0, "currency": "USD", "is_remote": false, "job_level": "", "job_function": "", "listing_type": "", "emails": "", "description": "* Experience as lead technical architect on technical projects performing systems architecture, engineering, administration, configuration, troubleshooting, performance tuning, preventative maintenance and security procedures.\n* Experience using Microsoft Visual Studio to develop n\\-tier web browser\\-based applications in ASP.Net/MVC and/or C\\# for n\\-tier web deployment.\n* Experience working with Servers, Systems and Infrastructure, Integrating equipments/IoT devices with applications, Cloud technologies, troubleshooting Web Application Firewall and Network layer issues.\n* Experience using Artificial Intelligence/Machine Language (AI/ML), Python to develop chatbot and other applications components for web deployment\n* Experience using PL/SQL to develop Oracle packages, triggers, stored procedures, functions, scripts and cursors.\n* Experience with Service Oriented Architecture (SOA) application integration including development of secure .Net web\\-services using Windows Communication Foundation (WCF), REST Services (Web API), message processing and Enterprise Service Bus.\n* Experience with automation and IaC tools like Terraform or Ansible\n* Experience coding and maintaining applications which contain Health Care data that fall under HIPAA Protected Health Information (PHI) along with HL7 Transformation.\n* AWS Certified Solutions Architect – Professional\n\nJob Types: Full\\-time, Contract\n\nPay: $85\\.00 \\- $90\\.00 per hour\n\nWork Location: In person", "company_industry": "", "company_url": "https://www.indeed.com/cmp/Pat-N-Sally-Inc", "company_logo": "", "company_url_direct": "", "company_addresses": "", "company_num_employees": "", "company_revenue": "", "company_description": "", "skills": "", "experience_range": "", "company_rating": "", "company_reviews_count": "", "vacancy_count": "", "work_from_home_type": ""}</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>.NET开发工程师</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>[".NET", "ASP.NET", "Ansible", "C#", "HL7", "IaC", "IoT", "MVC", "Oracle", "PL/SQL", "Python", "RESTful API", "SOA", "Terraform", "Visual Studio", "WCF", "机器学习"]</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>["n 层 Web 应用架构与开发", "AI/ML 聊天机器人开发", "Oracle PL/SQL 开发", "SOA 服务集成", "IaC 自动化部署"]</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>AI-ZCode</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/data/golden_set/review/jd_manual_review_merged.xlsx
+++ b/backend/data/golden_set/review/jd_manual_review_merged.xlsx
@@ -685,7 +685,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>["AIGC", "Prompt", "大模型评测", "数据分析", "数据标注", "视频生成"]</t>
+          <t>["AIGC", "Prompt", "大模型评测", "数据分析", "数据标注", "视频生成", "音频生成"]</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>["Ansible", "ELK", "Git", "Grafana", "Jenkins", "Kubernetes", "Linux", "Prometheus", "Python", "Shell", "可观测性"]</t>
+          <t>["Ansible", "ELK", "Git", "Grafana", "Jenkins", "Kubernetes", "Linux", "Prometheus", "Python", "Shell", "可观测性", "容器编排"]</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>["A/B测试", "Apache Spark", "Elasticsearch", "Pandas", "PyTorch", "Python", "SQL", "Spark", "TensorFlow", "多模态模型", "大语言模型", "机器学习", "模型评估", "深度学习", "特征工程"]</t>
+          <t>["A/B测试", "Apache Spark", "CNN", "Elasticsearch", "GBDT", "LR", "Pandas", "PyTorch", "Python", "RNN", "SQL", "Spark", "TensorFlow", "Transformer", "多模态模型", "大语言模型", "机器学习", "模型架构", "模型融合", "模型评估", "深度学习", "特征工程"]</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>["Python", "C++", "大语言模型", "LoRA", "增量预训练", "模型对齐", "PyTorch", "DeepSpeed", "Megatron", "vLLM", "TensorRT-LLM", "模型量化", "模型部署", "自然语言处理", "语音交互", "计算机视觉", "深度学习", "DeepSeek", "Qwen"]</t>
+          <t>["AGENT", "C++", "ChatBI", "DeepSeek", "DeepSpeed", "LoRA", "Megatron", "PyTorch", "Python", "Qwen", "TensorRT-LLM", "vLLM", "增量预训练", "多模态模型", "大语言模型", "检索增强生成", "模型对齐", "模型部署", "模型量化", "深度学习", "自然语言处理", "计算机视觉", "语音交互"]</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>["系统运维","系统部署","监控管理","性能优化","问题分析","故障处理","电网业务知识"]</t>
+          <t>["性能优化", "性能调优", "故障处理", "电网业务知识", "监控管理", "系统运维", "系统部署", "问题分析"]</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>["AJAX", "Android", "Android开发", "Axios", "BOM", "CSS3", "DOM", "ESLint", "Flex", "Git", "Grid", "HTML5", "JavaScript", "Pinia", "Prettier", "RESTful API", "React Native", "Vite", "Vue", "Vue Router", "Vue.js", "Vuex", "Webpack", "iOS", "iOS开发", "响应式布局", "权限控制", "路由配置"]</t>
+          <t>["AJAX", "Android", "Android开发", "Axios", "BOM", "CSS3", "DOM", "ESLint", "Flex", "Git", "Grid", "HTML5", "JavaScript", "Pinia", "Prettier", "RESTful API", "React Native", "Vite", "Vue", "Vue Router", "Vue.js", "Vuex", "Webpack", "iOS", "iOS开发", "交互逻辑", "响应式布局", "数据渲染", "权限控制", "路由配置"]</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>["AGENT", "AWQ", "Agent", "Apache Kafka", "Chroma", "DeepSeek", "Docker", "Elasticsearch", "Embedding", "FastAPI", "Function Calling", "GLM", "GPTQ", "Hybrid Search", "Kafka", "Kubernetes", "LangChain", "LlamaIndex", "Milvus", "Multi-Agent", "PyTorch", "Python", "Qwen", "RAG", "RESTful API", "React", "Redis", "Reflexion", "SSE", "TGI", "Tool Calling", "Transformer", "WebSocket", "vLLM", "向量数据库", "大语言模型", "异步编程", "推理加速", "检索增强生成", "模型量化"]</t>
+          <t>["AGENT", "AWQ", "Agent", "Apache Kafka", "Chroma", "DeepSeek", "Docker", "Elasticsearch", "Embedding", "FastAPI", "Function Calling", "GLM", "GPTQ", "Hybrid Search", "INT4", "INT8", "Kafka", "Kubernetes", "LangChain", "LlamaIndex", "Milvus", "Multi-Agent", "PyTorch", "Python", "Qwen", "RAG", "RESTful API", "React", "Redis", "Reflexion", "SSE", "TGI", "Tool Calling", "Transformer", "WebSocket", "vLLM", "向量数据库", "大语言模型", "异步编程", "推理加速", "检索增强生成", "模型量化"]</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>["CTS", "Cadence", "ICC2", "Innovus", "Perl", "STA", "TCL", "Tcl", "布局布线", "平面规划", "数字后端设计", "时序分析", "时序收敛", "物理", "物理设计", "物理验证", "电源分析"]</t>
+          <t>["CTS", "Cadence", "ICC2", "Innovus", "P&amp;R", "Perl", "STA", "TCL", "Tcl", "布局布线", "平面规划", "数字后端", "数字后端设计", "时序分析", "时序收敛", "物理", "物理设计", "物理验证", "电源分析"]</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>["ByteTrack", "C++", "C/C++", "DeepSORT", "NCNN", "ONNX", "OpenCV", "PyTorch", "Python", "TensorRT", "YOLO", "剪枝", "去雾", "图像分割", "图像增强", "图像识别", "多目标跟踪", "模型量化", "特征提取", "目标检测", "目标跟踪", "防抖", "障碍物识别"]</t>
+          <t>["ByteTrack", "C++", "C/C++", "CNN", "DeepSORT", "NCNN", "ONNX", "OpenCV", "PyTorch", "Python", "TensorRT", "Transformer", "YOLO", "剪枝", "去雾", "图像分割", "图像增强", "图像识别", "多目标跟踪", "模型量化", "特征提取", "目标检测", "目标跟踪", "防抖", "障碍物识别"]</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>["Excel", "Numpy", "PPT", "Pandas", "Python", "SQL", "指标体系", "数仓建模", "数据仓库", "数据分析", "数据可视化", "数据建模", "数据清洗", "数据透视", "统计学"]</t>
+          <t>["BI报表", "Excel", "Numpy", "PPT", "SQL", "指标体系", "指标体系搭建", "数仓建模", "数据仓库", "数据仓库建模", "数据分析", "数据可视化", "数据建模", "数据清洗", "数据透视", "统计学"]</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>["BI","数据挖掘","指标体系"]</t>
+          <t>["BI", "数据挖掘", "指标体系", "Python", "NumPy", "Pandas"]</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>["Agent", "Docker", "FastAPI", "LangChain", "LlamaIndex", "LoRA", "Milvus", "MySQL", "NLP", "OCR", "OpenAI API", "PGVector", "Prompt工程", "PyTorch", "Python", "QLoRA", "RAG", "Redis", "TensorFlow", "pgvector", "向量检索", "大模型", "大语言模型", "提示工程", "检索增强生成", "自然语言处理"]</t>
+          <t>["Agent", "Agent开发", "DeepSeek", "Docker", "FastAPI", "LangChain", "Llama", "LlamaIndex", "LoRA", "Milvus", "MySQL", "NLP", "OCR", "OpenAI", "OpenAI API", "PGVector", "Prompt工程", "PyTorch", "Python", "QLoRA", "Qwen", "RAG", "Redis", "TensorFlow", "pgvector", "向量检索", "大模型", "大语言模型", "提示工程", "数据治理", "文心一言", "文档切片", "检索增强生成", "自然语言处理", "通义千问", "重排序"]</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>["软件测试","自动化测试","Python","Java","大模型"]</t>
+          <t>["Java", "Python", "大模型", "大语言模型", "性能测试", "自动化测试", "软件测试"]</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>["C++", "C/C++", "CLIP", "CNN", "GAN", "Java", "OpenCV", "Python", "SAM", "Transformer", "图像分割", "图像分类", "图像处理", "图像生成", "大语言模型", "扩散模型", "模型训练", "模型轻量化", "目标检测"]</t>
+          <t>["C", "C++", "C/C++", "CLIP", "CNN", "GAN", "GitHub", "Java", "OpenCV", "Python", "SAM", "Transformer", "图像分割", "图像分类", "图像处理", "图像生成", "大语言模型", "扩散模型", "模型训练", "模型轻量化", "目标检测"]</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>["GIS", "GeoServer", "GeoWebCache", "Hadoop", "IO", "InfluxDB", "JVM调优", "Java", "MongoDB", "MyBatis", "MySQL", "MySQL Spatial", "Oracle Spatial", "PostGIS", "PostgreSQL", "RESTful API", "Redis", "Spring Boot", "Spring Cloud", "TDengine", "叠加分析", "多线程", "容器化", "数据格式解析", "消息", "空间查询", "空间索引", "缓冲区分析", "集合", "集合框架"]</t>
+          <t>["GIS", "GeoServer", "GeoWebCache", "Hadoop", "IO", "InfluxDB", "JVM调优", "Java", "MongoDB", "MyBatis", "MySQL", "MySQL Spatial", "Oracle Spatial", "PostGIS", "PostgreSQL", "RESTful API", "Redis", "Spring Boot", "Spring Cloud", "TDengine", "叠加分析", "多线程", "容器化", "数据格式解析", "查询性能", "消息", "空间查询", "空间索引", "系统架构调优", "缓冲区分析", "集合", "集合框架"]</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>["Docker", "FAISS", "Kubernetes", "Milvus", "RAG", "向量数据库", "大语言模型", "推理优化", "检索增强生成", "模型微调"]</t>
+          <t>["Docker", "FAISS", "Kubernetes", "Milvus", "RAG", "向量数据库", "大语言模型", "推理优化", "数据治理", "检索增强生成", "模型微调", "项目管理"]</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>["AGENT", "Agent", "CAE", "GNN", "PINN", "RAG", "VLM", "优化", "向量检索", "多模态模型", "大语言模型", "推理优化", "数据治理", "有限元仿真", "检索增强生成", "模型对齐", "模型微调", "知识图谱"]</t>
+          <t>["AGENT", "Agent", "CAE", "GNN", "PINN", "RAG", "VLM", "代理模型", "优化", "向量检索", "多模态模型", "大语言模型", "工业数据治理", "工具调用", "推理优化", "数据安全", "数据治理", "有限元仿真", "检索增强生成", "模型对齐", "模型工程化", "模型微调", "知识图谱", "系统集成"]</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>["AWS", "CI/CD", "CSS3", "Cypress", "Git", "GitHub", "HTML5", "JavaScript", "Jest", "Next.js", "Playwright", "RESTful API", "React", "React.js", "TypeScript"]</t>
+          <t>["AWS", "Agile", "CI/CD", "CSS3", "Cypress", "Git", "GitHub", "HTML5", "JavaScript", "Jest", "Next.js", "Playwright", "RESTful API", "React", "React.js", "TypeScript"]</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>["AWS", "Android", "Android开发", "Azure", "CI/CD", "Detox", "DevOps", "GCP", "Java", "Jest", "Kotlin", "Maestro", "Objective-C", "React Native", "React Native Testing Library", "Swift", "iOS", "iOS开发", "自动化测试"]</t>
+          <t>["AWS", "Android", "Android开发", "Azure", "CI/CD", "Detox", "DevOps", "Fabric", "GCP", "Hermes", "JSI", "Java", "Jest", "Kotlin", "Maestro", "Objective-C", "React Native", "React Native Testing Library", "Swift", "TurboModules", "iOS", "iOS开发", "自动化测试"]</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>[".NET", "ASP.NET", "Ansible", "C#", "HL7", "IaC", "IoT", "MVC", "Oracle", "PL/SQL", "Python", "RESTful API", "SOA", "Terraform", "Visual Studio", "WCF", "机器学习"]</t>
+          <t>[".NET", "AI", "ASP.NET", "Ansible", "C#", "HL7", "IaC", "IoT", "ML", "MVC", "Oracle", "PL/SQL", "Python", "REST", "RESTful API", "SOA", "Terraform", "Visual Studio", "WCF", "Web API", "机器学习"]</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
